--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14467.2998046875</v>
+        <v>14235.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.03370027511297802</v>
+        <v>0.04820507590047729</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.05569905171391554</v>
+        <v>0.03880617372208839</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02199877660093752</v>
+        <v>0.009398902178388902</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Altı</t>
+          <t>Karda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.97999954223633</v>
+        <v>39.40000152587891</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.02550001144409175</v>
+        <v>-0.01499996185302732</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32483.3329518636</v>
+        <v>32833.33460489909</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-850.0003814697266</v>
+        <v>-499.9987284342424</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.06000137329102</v>
+        <v>44.97999954223633</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.0316483214661315</v>
+        <v>-0.01142858148931147</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32278.38928446228</v>
+        <v>32952.38061702294</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1054.94404887105</v>
+        <v>-380.9527163103849</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>430</v>
+        <v>434.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1582491582491583</v>
+        <v>0.1710437710437711</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38608.30527497194</v>
+        <v>39034.79236812569</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5274.971941638607</v>
+        <v>5701.459034792366</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1215,10 +1215,10 @@
         <v>101665.535802718</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0151796588900126</v>
+        <v>-0.01517965889001283</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718043</v>
+        <v>0.01665535802718021</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989486</v>
+        <v>-0.05854166473989508</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101579.9132001645</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008421989013038811</v>
+        <v>-0.000842198901303659</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.01579913200164529</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493741</v>
+        <v>99903.87102493743</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044318</v>
+        <v>-0.007105427940044096</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506259266</v>
+        <v>-0.0009612897506257045</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049301</v>
+        <v>-0.04672896308049279</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99725.18443384963</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00178858525955583</v>
+        <v>-0.001788585259556053</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.00274815566150366</v>
@@ -1353,10 +1353,10 @@
         <v>100567.2965303391</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284487</v>
+        <v>-0.01333614376284464</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.005672965303390898</v>
+        <v>0.00567296530339112</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494105</v>
+        <v>-0.02929494153494083</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98982.15764175884</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685612</v>
+        <v>-0.01576197176685634</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01017842358241161</v>
@@ -1402,7 +1402,7 @@
         <v>0.003127667249263499</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055236009</v>
+        <v>-0.007082591055235898</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669556011</v>
+        <v>-0.05426586669555999</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98699.49739704847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087438</v>
+        <v>-0.005964680366087549</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01300502602951525</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463837</v>
+        <v>97511.54763463838</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704539</v>
+        <v>-0.02101826087704517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361637</v>
+        <v>-0.02488452365361615</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717159</v>
+        <v>-0.06034862172717137</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>97085.90440793287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770521</v>
+        <v>-0.004365054570770743</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.02914095592067123</v>
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699691</v>
+        <v>101364.3995699692</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189433</v>
+        <v>0.02123082912189456</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969144</v>
+        <v>0.01364399569969166</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01379324890042533</v>
+        <v>-0.0137932489004251</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105261.7030227777</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0384484441218278</v>
+        <v>0.03844844412182757</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05261703022777731</v>
@@ -1675,10 +1675,10 @@
         <v>104848.7672438694</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059834</v>
+        <v>0.02469452791059856</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869401</v>
+        <v>0.04848767243869423</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549497</v>
+        <v>0.02170717039549519</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>102169.894507684</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636639</v>
+        <v>-0.02554987346636661</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.02169894507684034</v>
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.8983480134</v>
+        <v>94222.89834801342</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161273</v>
+        <v>-0.009506854050161162</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986594</v>
+        <v>-0.05777101651986583</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613263</v>
+        <v>-0.08901004230613252</v>
       </c>
     </row>
     <row r="57">
@@ -2158,7 +2158,7 @@
         <v>95707.04281032382</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844455</v>
+        <v>0.01575142017844433</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>-0.04292957189676172</v>
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98649.26988175404</v>
+        <v>98649.26988175407</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006384731412490963</v>
+        <v>-0.006384731412490741</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01350730118245957</v>
+        <v>-0.01350730118245935</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07710187211065578</v>
+        <v>-0.07710187211065556</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99346.32347202346</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007065978198368406</v>
+        <v>0.007065978198368184</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.006536765279765322</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97750.83563441616</v>
+        <v>97750.83563441614</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01605985789757591</v>
+        <v>-0.01605985789757602</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02249164365583844</v>
+        <v>-0.02249164365583856</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.06847089127514661</v>
+        <v>-0.06847089127514672</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>97120.46162594971</v>
+        <v>97120.4616259497</v>
       </c>
       <c r="C67" s="4" t="n">
         <v>-0.006448783832641802</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.02879538374050294</v>
+        <v>-0.02879538374050306</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06710536622736807</v>
+        <v>-0.06710536622736818</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96453.88939779936</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006863355229071999</v>
+        <v>-0.006863355229071888</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03546110602200647</v>
@@ -2569,13 +2569,13 @@
         <v>46276</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>103370.0275112978</v>
+        <v>104820.5075900477</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0</v>
+        <v>0.01403192118325958</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>0.03370027511297824</v>
+        <v>0.04820507590047729</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>14467.2998046875</v>
@@ -2584,11 +2584,34 @@
         <v>0.05569905171391554</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>-0.0219987766009373</v>
+        <v>-0.007493975813438247</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>104820.5075900477</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0.04820507590047729</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>14235.7998046875</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0.03880617372208839</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0.009398902178388902</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G75"/>
+  <autoFilter ref="A1:G76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14235.7998046875</v>
+        <v>13892.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.04820507590047729</v>
+        <v>0.02851976645960086</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.03880617372208839</v>
+        <v>0.01374049946639677</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.009398902178388902</v>
+        <v>0.01477926699320409</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>39.40000152587891</v>
+        <v>38.86000061035156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.01499996185302732</v>
+        <v>-0.02849998474121096</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32833.33460489909</v>
+        <v>32383.33384195963</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-499.9987284342424</v>
+        <v>-949.9994913736991</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>44.97999954223633</v>
+        <v>43.52000045776367</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.01142858148931147</v>
+        <v>-0.0435164734557435</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>32952.38061702294</v>
+        <v>31882.78421814188</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-380.9527163103849</v>
+        <v>-1450.54911519145</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>434.75</v>
+        <v>429.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1710437710437711</v>
+        <v>0.1575757575757575</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>39034.79236812569</v>
+        <v>38585.85858585858</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5701.459034792366</v>
+        <v>5252.525252525251</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2592,13 +2592,13 @@
         <v>46279</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>104820.5075900477</v>
+        <v>102851.9766459601</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0</v>
+        <v>-0.01878001728236767</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.04820507590047729</v>
+        <v>0.02851976645960086</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,11 +2607,34 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.009398902178388902</v>
+        <v>-0.01028640726248753</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>102851.9766459601</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>0.02851976645960086</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>13892.2998046875</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0.01374049946639677</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0.01477926699320409</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G76"/>
+  <autoFilter ref="A1:G77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ABOVE_MA200_RISK_ON</t>
+          <t>BELOW_MA200_DEFENSIVE</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13892.2998046875</v>
+        <v>13122.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02851976645960086</v>
+        <v>0.000499812191191662</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.01374049946639677</v>
+        <v>-0.04242559768133392</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.01477926699320409</v>
+        <v>0.04292540987252558</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.86000061035156</v>
+        <v>38.2599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.02849998474121096</v>
+        <v>-0.0435000419616699</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32383.33384195963</v>
+        <v>31883.331934611</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-949.9994913736991</v>
+        <v>-1450.001398722328</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43.52000045776367</v>
+        <v>42.40000152587891</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.0435164734557435</v>
+        <v>-0.06813183459606797</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31882.78421814188</v>
+        <v>31062.27218013106</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-1450.54911519145</v>
+        <v>-2271.061153202267</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>429.75</v>
+        <v>413.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1575757575757575</v>
+        <v>0.1131313131313132</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38585.85858585858</v>
+        <v>37104.3771043771</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5252.525252525251</v>
+        <v>3771.043771043769</v>
       </c>
     </row>
   </sheetData>
@@ -836,16 +836,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102223.0027697347</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02223002769734705</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02223002769734705</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01397839285960711</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -936,13 +936,13 @@
         <v>46176</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>101548.9054270188</v>
+        <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006594380173260195</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.01548905427018843</v>
+        <v>0.01344265713915593</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>13965.7001953125</v>
@@ -951,7 +951,7 @@
         <v>0.01909662837948778</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.00360757410929935</v>
+        <v>-0.005653971240331845</v>
       </c>
     </row>
     <row r="5">
@@ -959,13 +959,13 @@
         <v>46177</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>100052.2803667449</v>
+        <v>99851.93983030412</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>-0.01473797333393734</v>
+        <v>-0.01472531152205636</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.0005228036674491676</v>
+        <v>-0.001480601696958739</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>13872.2998046875</v>
@@ -974,7 +974,7 @@
         <v>0.01228107156213509</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01175826789468593</v>
+        <v>-0.01376167325909383</v>
       </c>
     </row>
     <row r="6">
@@ -982,13 +982,13 @@
         <v>46178</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99150.39483732327</v>
+        <v>98947.76907887068</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.009014142667371106</v>
+        <v>-0.009055114532277031</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.008496051626767365</v>
+        <v>-0.01052230921129316</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>13694.2001953125</v>
@@ -997,7 +997,7 @@
         <v>-0.0007151054208625052</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.00778094620590486</v>
+        <v>-0.009807203790430652</v>
       </c>
     </row>
     <row r="7">
@@ -1005,13 +1005,13 @@
         <v>46181</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>99194.90173474306</v>
+        <v>98992.27597629049</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.000448882704832565</v>
+        <v>0.0004498019291807598</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.008050982652569316</v>
+        <v>-0.01007724023709511</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>13860.599609375</v>
@@ -1020,7 +1020,7 @@
         <v>0.01142729198591641</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.01947827463848573</v>
+        <v>-0.02150453222301152</v>
       </c>
     </row>
     <row r="8">
@@ -1028,13 +1028,13 @@
         <v>46182</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>98960.65707117392</v>
+        <v>98754.54045799351</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.002361458698709518</v>
+        <v>-0.002401556242164982</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.01039342928826081</v>
+        <v>-0.01245459542006488</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>13741.900390625</v>
@@ -1043,7 +1043,7 @@
         <v>0.002765644383026844</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01315907367128766</v>
+        <v>-0.01522023980309173</v>
       </c>
     </row>
     <row r="9">
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98567.79623824963</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003969868880738581</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01432203761750372</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01728464775870342</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97972.1929521213</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006042574845527504</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02027807047878705</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02316044058970346</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1097,13 +1097,13 @@
         <v>46185</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>99533.39140527607</v>
+        <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01593511797697267</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.004666085947239274</v>
+        <v>-0.006707112532536752</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>13938.5</v>
@@ -1112,7 +1112,7 @@
         <v>0.01711179217746639</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.02177787812470566</v>
+        <v>-0.02381890471000314</v>
       </c>
     </row>
     <row r="12">
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102685.3605150107</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03166745416018824</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02685360515010737</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02732038716053187</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1143,13 +1143,13 @@
         <v>46189</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>101717.1238252686</v>
+        <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009429159958985744</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.01717123825268585</v>
+        <v>0.0150979883929776</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>14493.099609375</v>
@@ -1158,7 +1158,7 @@
         <v>0.05758169945818747</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.04041046120550162</v>
+        <v>-0.04248371106520987</v>
       </c>
     </row>
     <row r="14">
@@ -1166,13 +1166,13 @@
         <v>46190</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>100070.5429599663</v>
+        <v>99864.02903600449</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.01618784333826406</v>
+        <v>-0.01621291562106952</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.0007054295996633542</v>
+        <v>-0.001359709639955131</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>14421.2001953125</v>
@@ -1181,7 +1181,7 @@
         <v>0.05233509889904409</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.05162966929938073</v>
+        <v>-0.05369480853899922</v>
       </c>
     </row>
     <row r="15">
@@ -1189,13 +1189,13 @@
         <v>46191</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>103232.5710170966</v>
+        <v>103021.0619375862</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.03159799041357481</v>
+        <v>0.03161331394353706</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.03232571017096575</v>
+        <v>0.030210619375862</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>14827.400390625</v>
@@ -1204,7 +1204,7 @@
         <v>0.08197609388682126</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.04965038371585551</v>
+        <v>-0.05176547451095925</v>
       </c>
     </row>
     <row r="16">
@@ -1212,13 +1212,13 @@
         <v>46192</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>101665.535802718</v>
+        <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01517965889001283</v>
+        <v>-0.01516627338573839</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01665535802718021</v>
+        <v>0.01458616347751684</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.05854166473989508</v>
+        <v>-0.06061085928955845</v>
       </c>
     </row>
     <row r="17">
@@ -1235,13 +1235,13 @@
         <v>46195</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>101579.9132001645</v>
+        <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.000842198901303659</v>
+        <v>-0.0008213118147898379</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.01579913200164529</v>
+        <v>0.0137528718743305</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>14729.7001953125</v>
@@ -1250,7 +1250,7 @@
         <v>0.07484677432227826</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.05904764232063298</v>
+        <v>-0.06109390244794777</v>
       </c>
     </row>
     <row r="18">
@@ -1258,13 +1258,13 @@
         <v>46196</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>100618.810734021</v>
+        <v>100412.1625464157</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.009461540533606483</v>
+        <v>-0.009500586067259009</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.00618810734020947</v>
+        <v>0.004121625464157397</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>14539.599609375</v>
@@ -1273,7 +1273,7 @@
         <v>0.06097486933559537</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.0547867619953859</v>
+        <v>-0.05685324387143798</v>
       </c>
     </row>
     <row r="19">
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99903.87102493743</v>
+        <v>99701.94672551964</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007105427940044096</v>
+        <v>-0.007073005927621612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.0009612897506257045</v>
+        <v>-0.002980532744803588</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04672896308049279</v>
+        <v>-0.04874820607467067</v>
       </c>
     </row>
     <row r="20">
@@ -1304,13 +1304,13 @@
         <v>46198</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>99725.18443384963</v>
+        <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001788585259556053</v>
+        <v>-0.00180034251077299</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.00274815566150366</v>
+        <v>-0.004775509275771306</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>14259.7998046875</v>
@@ -1319,7 +1319,7 @@
         <v>0.04055748720720231</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.04330564286870597</v>
+        <v>-0.04533299648297362</v>
       </c>
     </row>
     <row r="21">
@@ -1327,13 +1327,13 @@
         <v>46199</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>101926.6043796041</v>
+        <v>101724.4088128252</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.02207486462173192</v>
+        <v>0.0221252567729715</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.01926604379604102</v>
+        <v>0.01724408812825207</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>14274</v>
@@ -1342,7 +1342,7 @@
         <v>0.04159369527145351</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.02232765147541249</v>
+        <v>-0.02434960714320145</v>
       </c>
     </row>
     <row r="22">
@@ -1350,13 +1350,13 @@
         <v>46202</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>100567.2965303391</v>
+        <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01333614376284464</v>
+        <v>-0.01334406573409486</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00567296530339112</v>
+        <v>0.00366991614864931</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.02929494153494083</v>
+        <v>-0.03129799068968264</v>
       </c>
     </row>
     <row r="23">
@@ -1373,13 +1373,13 @@
         <v>46203</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>98982.15764175884</v>
+        <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576197176685634</v>
+        <v>-0.01576249680180841</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.01017842358241161</v>
+        <v>-0.01215042769471508</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>14121.7998046875</v>
@@ -1388,7 +1388,7 @@
         <v>0.03048743466779769</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.0406658582502093</v>
+        <v>-0.04263786236251277</v>
       </c>
     </row>
     <row r="24">
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99291.7408944764</v>
+        <v>99094.94601425054</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.003127667249263499</v>
+        <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.007082591055235898</v>
+        <v>-0.009050539857494599</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05426586669555999</v>
+        <v>-0.0562338154978187</v>
       </c>
     </row>
     <row r="25">
@@ -1419,13 +1419,13 @@
         <v>46205</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>98699.49739704847</v>
+        <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005964680366087549</v>
+        <v>-0.00593839502983573</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.01300502602951525</v>
+        <v>-0.01493518920642323</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>14455</v>
@@ -1434,7 +1434,7 @@
         <v>0.05480151780502052</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.06780654383453577</v>
+        <v>-0.06973670701144374</v>
       </c>
     </row>
     <row r="26">
@@ -1442,13 +1442,13 @@
         <v>46206</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>97954.05404427544</v>
+        <v>97761.3062538714</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.007552656015807901</v>
+        <v>-0.007564728912465735</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.0204594595572456</v>
+        <v>-0.02238693746128595</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>14417.900390625</v>
@@ -1457,7 +1457,7 @@
         <v>0.05209430754706657</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.07255376710431216</v>
+        <v>-0.07448124500835251</v>
       </c>
     </row>
     <row r="27">
@@ -1465,13 +1465,13 @@
         <v>46209</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>99764.36654381154</v>
+        <v>99564.06162833737</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.01848124120230743</v>
+        <v>0.01844037731845027</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.002356334561884554</v>
+        <v>-0.004359383716626364</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>14424.5</v>
@@ -1480,7 +1480,7 @@
         <v>0.05257589025102161</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.05493222481290616</v>
+        <v>-0.05693527396764797</v>
       </c>
     </row>
     <row r="28">
@@ -1488,13 +1488,13 @@
         <v>46210</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>99605.07304456622</v>
+        <v>99403.01174143069</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.001596697345593534</v>
+        <v>-0.001617550391906031</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.003949269554337831</v>
+        <v>-0.005969882585693087</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>14497.400390625</v>
@@ -1503,7 +1503,7 @@
         <v>0.05789553346650611</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.06184480302084394</v>
+        <v>-0.0638654160521992</v>
       </c>
     </row>
     <row r="29">
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97511.54763463838</v>
+        <v>97308.67800956823</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02101826087704517</v>
+        <v>-0.02106911747614126</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02488452365361615</v>
+        <v>-0.02691321990431761</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06034862172717137</v>
+        <v>-0.06237731797787283</v>
       </c>
     </row>
     <row r="30">
@@ -1534,13 +1534,13 @@
         <v>46212</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>97085.90440793287</v>
+        <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004365054570770743</v>
+        <v>-0.004314514982734163</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02914095592067123</v>
+        <v>-0.031111617396541</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>14105.400390625</v>
@@ -1549,7 +1549,7 @@
         <v>0.02929074654298014</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.05843170246365137</v>
+        <v>-0.06040236393952114</v>
       </c>
     </row>
     <row r="31">
@@ -1557,13 +1557,13 @@
         <v>46213</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>98936.40953523434</v>
+        <v>98735.29355775118</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.01906049223712292</v>
+        <v>0.01905746142237508</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.01063590464765651</v>
+        <v>-0.0126470644224882</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>14321.2001953125</v>
@@ -1572,7 +1572,7 @@
         <v>0.04503795937773636</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.05567386402539287</v>
+        <v>-0.05768502380022456</v>
       </c>
     </row>
     <row r="32">
@@ -1580,13 +1580,13 @@
         <v>46216</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>99257.08926857149</v>
+        <v>99055.02796543598</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.003241271184628358</v>
+        <v>0.003238299053597959</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.007429107314285033</v>
+        <v>-0.009449720345640289</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>14092</v>
@@ -1595,7 +1595,7 @@
         <v>0.02831290134267372</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.03574200865695876</v>
+        <v>-0.03776262168831401</v>
       </c>
     </row>
     <row r="33">
@@ -1603,13 +1603,13 @@
         <v>46217</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>101364.3995699692</v>
+        <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02123082912189456</v>
+        <v>0.02121828779866686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01364399569969166</v>
+        <v>0.01156806056711579</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0137932489004251</v>
+        <v>-0.01586918403300097</v>
       </c>
     </row>
     <row r="34">
@@ -1626,13 +1626,13 @@
         <v>46219</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>105261.7030227777</v>
+        <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03844844412182757</v>
+        <v>0.03846461342820384</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.05261703022777731</v>
+        <v>0.05047763497314772</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>14251.2998046875</v>
@@ -1641,7 +1641,7 @@
         <v>0.0399372303478911</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.01267979987988621</v>
+        <v>0.01054040462525663</v>
       </c>
     </row>
     <row r="35">
@@ -1649,13 +1649,13 @@
         <v>46220</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>102321.9743913936</v>
+        <v>102113.5698161271</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.02792780799630412</v>
+        <v>-0.02793199572747407</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.02321974391393611</v>
+        <v>0.0211356981612707</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>13981.099609375</v>
@@ -1664,7 +1664,7 @@
         <v>0.02022034510909232</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.002999398804843789</v>
+        <v>0.0009153530521783804</v>
       </c>
     </row>
     <row r="36">
@@ -1672,13 +1672,13 @@
         <v>46223</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>104848.7672438694</v>
+        <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02469452791059856</v>
+        <v>0.02467092015235539</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04848767243869423</v>
+        <v>0.04632805543532714</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.02170717039549519</v>
+        <v>0.0195475533921281</v>
       </c>
     </row>
     <row r="37">
@@ -1695,13 +1695,13 @@
         <v>46224</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>102169.894507684</v>
+        <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02554987346636661</v>
+        <v>-0.02556649570614189</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.02169894507684034</v>
+        <v>0.01957711369882409</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>13974.099609375</v>
@@ -1710,7 +1710,7 @@
         <v>0.01970954534260061</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.001989399734239727</v>
+        <v>-0.0001324316437765205</v>
       </c>
     </row>
     <row r="38">
@@ -1718,13 +1718,13 @@
         <v>46225</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>103048.3004645202</v>
+        <v>102832.4730278269</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.008597502826726222</v>
+        <v>0.008579651761414953</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.03048300464520159</v>
+        <v>0.02832473027826854</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>14138.900390625</v>
@@ -1733,7 +1733,7 @@
         <v>0.03173528828261829</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.001252283637416696</v>
+        <v>-0.003410558004349751</v>
       </c>
     </row>
     <row r="39">
@@ -1741,13 +1741,13 @@
         <v>46226</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>103895.0625877499</v>
+        <v>103684.2275665308</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.008217138171253247</v>
+        <v>0.008282933528919845</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>0.03895062587749942</v>
+        <v>0.03684227566530796</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>14077.7001953125</v>
@@ -1756,7 +1756,7 @@
         <v>0.02726942464335225</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.01168120123414718</v>
+        <v>0.009572851021955708</v>
       </c>
     </row>
     <row r="40">
@@ -1764,13 +1764,13 @@
         <v>46227</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>102017.60225892</v>
+        <v>101812.3021878973</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.01807073678062643</v>
+        <v>-0.01805409966942528</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.02017602258920004</v>
+        <v>0.01812302187897274</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>13943.900390625</v>
@@ -1779,7 +1779,7 @@
         <v>0.01750586621606831</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.002670156373131727</v>
+        <v>0.0006171556629044339</v>
       </c>
     </row>
     <row r="41">
@@ -1787,13 +1787,13 @@
         <v>46230</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>101933.2998138635</v>
+        <v>101726.3803588972</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>-0.0008263519548568077</v>
+        <v>-0.0008439238397880411</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.01933299813863543</v>
+        <v>0.01726380358897206</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>13774.7998046875</v>
@@ -1802,7 +1802,7 @@
         <v>0.005166360528860103</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.01416663760977532</v>
+        <v>0.01209744306011196</v>
       </c>
     </row>
     <row r="42">
@@ -1810,13 +1810,13 @@
         <v>46231</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>102672.1256327757</v>
+        <v>102461.8331462788</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.007248130103325812</v>
+        <v>0.007229715485667532</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.02672125632775746</v>
+        <v>0.02461833146278836</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>13687.900390625</v>
@@ -1825,7 +1825,7 @@
         <v>-0.001174810958479267</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.02789606728623673</v>
+        <v>0.02579314242126762</v>
       </c>
     </row>
     <row r="43">
@@ -1833,13 +1833,13 @@
         <v>46232</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>101321.2626725588</v>
+        <v>101112.5895700055</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>-0.01315705652231813</v>
+        <v>-0.01316825528923671</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.01321262672558765</v>
+        <v>0.01112589570005462</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>13501.599609375</v>
@@ -1848,7 +1848,7 @@
         <v>-0.01476943889557791</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.02798206562116556</v>
+        <v>0.02589533459563254</v>
       </c>
     </row>
     <row r="44">
@@ -1856,13 +1856,13 @@
         <v>46233</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>100007.3767240604</v>
+        <v>99800.59153273748</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.01296752442519822</v>
+        <v>-0.01297561503317657</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>7.376724060437212e-05</v>
+        <v>-0.001994084672625185</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>13292.900390625</v>
@@ -1871,7 +1871,7 @@
         <v>-0.02999851206764448</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.03007227930824885</v>
+        <v>0.02800442739501929</v>
       </c>
     </row>
     <row r="45">
@@ -1879,13 +1879,13 @@
         <v>46234</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>101068.0382772884</v>
+        <v>100857.340259787</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.01060583316923247</v>
+        <v>0.01058860183912724</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.01068038277288408</v>
+        <v>0.008573402597870095</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>13458.099609375</v>
@@ -1894,7 +1894,7 @@
         <v>-0.01794369458734679</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.02862407736023087</v>
+        <v>0.02651709718521689</v>
       </c>
     </row>
     <row r="46">
@@ -1902,13 +1902,13 @@
         <v>46237</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>98817.64242294777</v>
+        <v>98613.0164102163</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0222661475645396</v>
+        <v>-0.0222524592041573</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.01182357577052229</v>
+        <v>-0.01386983589783708</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>13410.5</v>
@@ -1917,7 +1917,7 @@
         <v>-0.02141710449503798</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.009593528724515688</v>
+        <v>0.007547268597200896</v>
       </c>
     </row>
     <row r="47">
@@ -1925,13 +1925,13 @@
         <v>46238</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>100510.1501194647</v>
+        <v>100301.8798078415</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.01712758627930899</v>
+        <v>0.01712617115979698</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>0.00510150119464714</v>
+        <v>0.003018798078415319</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>13687.900390625</v>
@@ -1940,7 +1940,7 @@
         <v>-0.001174810958479267</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.006276312153126407</v>
+        <v>0.004193609036894586</v>
       </c>
     </row>
     <row r="48">
@@ -1948,13 +1948,13 @@
         <v>46239</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>100395.8946916857</v>
+        <v>100189.5150313672</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.001136755120186628</v>
+        <v>-0.001120265908172269</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>0.003958946916856831</v>
+        <v>0.001895150313672156</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>13703.099609375</v>
@@ -1963,7 +1963,7 @@
         <v>-6.570276014306042e-05</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.004024649676999892</v>
+        <v>0.001960853073815216</v>
       </c>
     </row>
     <row r="49">
@@ -1971,13 +1971,13 @@
         <v>46240</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>99635.64159588418</v>
+        <v>99429.26193556572</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>-0.007572551628094226</v>
+        <v>-0.007588150272645589</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>-0.003643584041158165</v>
+        <v>-0.005707380644342841</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>13798.7998046875</v>
@@ -1986,7 +1986,7 @@
         <v>0.006917674013974029</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-0.01056125805513219</v>
+        <v>-0.01262505465831687</v>
       </c>
     </row>
     <row r="50">
@@ -1994,13 +1994,13 @@
         <v>46241</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>97154.28928705474</v>
+        <v>96946.01897543157</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.02490426386667588</v>
+        <v>-0.02497497126895498</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.0284571071294526</v>
+        <v>-0.03053981024568442</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>13779.400390625</v>
@@ -2009,7 +2009,7 @@
         <v>0.005502071703517242</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.03395917883296984</v>
+        <v>-0.03604188194920166</v>
       </c>
     </row>
     <row r="51">
@@ -2017,13 +2017,13 @@
         <v>46244</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>95622.17344357757</v>
+        <v>95414.71419396337</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>-0.01576992487640283</v>
+        <v>-0.01579543747800771</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>-0.04377826556422426</v>
+        <v>-0.04585285806036621</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>13811.599609375</v>
@@ -2032,7 +2032,7 @@
         <v>0.007851693620475775</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-0.05162995918470004</v>
+        <v>-0.05370455168084198</v>
       </c>
     </row>
     <row r="52">
@@ -2040,13 +2040,13 @@
         <v>46245</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>94508.13507854677</v>
+        <v>94304.45439146763</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.01165041877748318</v>
+        <v>-0.0116361486996519</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.05491864921453238</v>
+        <v>-0.05695545608532371</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>13704.5</v>
@@ -2055,7 +2055,7 @@
         <v>3.648569760650311e-05</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.05495513491213888</v>
+        <v>-0.05699194178293021</v>
       </c>
     </row>
     <row r="53">
@@ -2063,13 +2063,13 @@
         <v>46246</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>95468.77340237095</v>
+        <v>95261.44841640015</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.01016460988279788</v>
+        <v>0.01014791964078321</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>-0.04531226597629046</v>
+        <v>-0.04738551583599859</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>14110.099609375</v>
@@ -2078,7 +2078,7 @@
         <v>0.029633655091579</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-0.07494592106786946</v>
+        <v>-0.0770191709275776</v>
       </c>
     </row>
     <row r="54">
@@ -2086,13 +2086,13 @@
         <v>46247</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>96176.8759284533</v>
+        <v>95973.60077237866</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.007417111384661057</v>
+        <v>0.007475766617211388</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.03823124071546702</v>
+        <v>-0.04026399227621336</v>
       </c>
       <c r="E54" s="5" t="n">
         <v>14132.2001953125</v>
@@ -2101,7 +2101,7 @@
         <v>0.03124636568246508</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.0694776063979321</v>
+        <v>-0.07151035795867844</v>
       </c>
     </row>
     <row r="55">
@@ -2109,13 +2109,13 @@
         <v>46248</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>95127.25931854667</v>
+        <v>94924.9294881244</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>-0.01091339887861864</v>
+        <v>-0.010926663955658</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>-0.04872740681453325</v>
+        <v>-0.05075070511875601</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>14172.2998046875</v>
@@ -2124,7 +2124,7 @@
         <v>0.03417249012605805</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-0.0828998969405913</v>
+        <v>-0.08492319524481406</v>
       </c>
     </row>
     <row r="56">
@@ -2132,13 +2132,13 @@
         <v>46251</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>94222.89834801342</v>
+        <v>94016.65295133834</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.009506854050161162</v>
+        <v>-0.009568366726041999</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.05777101651986583</v>
+        <v>-0.05983347048661658</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>14132.099609375</v>
@@ -2147,7 +2147,7 @@
         <v>0.03123902578626669</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.08901004230613252</v>
+        <v>-0.09107249627288327</v>
       </c>
     </row>
     <row r="57">
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95707.04281032382</v>
+        <v>95488.37939667342</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01575142017844433</v>
+        <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.04292957189676172</v>
+        <v>-0.04511620603326572</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07386944346710611</v>
+        <v>-0.07605607760361011</v>
       </c>
     </row>
     <row r="58">
@@ -2178,13 +2178,13 @@
         <v>46253</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>97317.06189679352</v>
+        <v>97092.18947465546</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.01682236791769331</v>
+        <v>0.01679586655586185</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.02682938103206478</v>
+        <v>-0.02907810525344534</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>14459</v>
@@ -2193,7 +2193,7 @@
         <v>0.05509340338587276</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.08192278441793754</v>
+        <v>-0.0841715086393181</v>
       </c>
     </row>
     <row r="59">
@@ -2201,13 +2201,13 @@
         <v>46254</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>97956.38493482044</v>
+        <v>97734.48275328283</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.00656948561296411</v>
+        <v>0.006615292971583697</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>-0.0204361506517956</v>
+        <v>-0.02265517246717164</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>14396.5</v>
@@ -2216,7 +2216,7 @@
         <v>0.05053269118505543</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-0.07096884183685104</v>
+        <v>-0.07318786365222707</v>
       </c>
     </row>
     <row r="60">
@@ -2224,13 +2224,13 @@
         <v>46255</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>98410.28723618698</v>
+        <v>98185.41481404894</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.004633718380568697</v>
+        <v>0.004613848132848153</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.01589712763813012</v>
+        <v>-0.01814585185951056</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>14514.7998046875</v>
@@ -2239,7 +2239,7 @@
         <v>0.05916519298653689</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.075062320624667</v>
+        <v>-0.07731104484604745</v>
       </c>
     </row>
     <row r="61">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97944.8116121026</v>
+        <v>97722.23537227376</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004729948841295739</v>
+        <v>-0.004717395579092787</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.020551883878974</v>
+        <v>-0.02277764627726242</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.07874657156140241</v>
+        <v>-0.08097233395969083</v>
       </c>
     </row>
     <row r="62">
@@ -2270,13 +2270,13 @@
         <v>46259</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>98436.88852787223</v>
+        <v>98211.47631108631</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.005024022280204266</v>
+        <v>0.005006444407956723</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.01563111472127776</v>
+        <v>-0.0178852368891369</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>14473.400390625</v>
@@ -2285,7 +2285,7 @@
         <v>0.05614421998139218</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.07177533470266995</v>
+        <v>-0.07402945687052909</v>
       </c>
     </row>
     <row r="63">
@@ -2293,13 +2293,13 @@
         <v>46260</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>99283.16623192659</v>
+        <v>99057.35122421054</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.008597160238509094</v>
+        <v>0.008612790937434944</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>-0.007168337680734105</v>
+        <v>-0.009426487757894675</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>14610.900390625</v>
@@ -2308,7 +2308,7 @@
         <v>0.06617778682319031</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-0.07334612450392441</v>
+        <v>-0.07560427458108498</v>
       </c>
     </row>
     <row r="64">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98649.26988175407</v>
+        <v>98425.88257991624</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006384731412490741</v>
+        <v>-0.006374778211714838</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01350730118245935</v>
+        <v>-0.01574117420083754</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07710187211065556</v>
+        <v>-0.07933574512903374</v>
       </c>
     </row>
     <row r="65">
@@ -2339,13 +2339,13 @@
         <v>46262</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>99346.32347202346</v>
+        <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007065978198368184</v>
+        <v>0.007072410694939357</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>-0.006536765279765322</v>
+        <v>-0.008780091554667191</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>14641.599609375</v>
@@ -2354,7 +2354,7 @@
         <v>0.06841795164732933</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-0.07495471692709466</v>
+        <v>-0.07719804320199652</v>
       </c>
     </row>
     <row r="66">
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97750.83563441614</v>
+        <v>97531.90369347899</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01605985789757602</v>
+        <v>-0.01604171927446696</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02249164365583856</v>
+        <v>-0.02468096306521006</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.06847089127514672</v>
+        <v>-0.07066021068451822</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>97120.4616259497</v>
+        <v>96900.04456471233</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006448783832641802</v>
+        <v>-0.006478486575556386</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.02879538374050306</v>
+        <v>-0.03099955435287671</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06710536622736818</v>
+        <v>-0.06930953683974184</v>
       </c>
     </row>
     <row r="68">
@@ -2408,13 +2408,13 @@
         <v>46267</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>96453.88939779936</v>
+        <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006863355229071888</v>
+        <v>-0.006867825931805349</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.03546110602200647</v>
+        <v>-0.03765448074142297</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>14050.599609375</v>
@@ -2423,7 +2423,7 @@
         <v>0.02529185707640114</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.06075296309840761</v>
+        <v>-0.06294633781782411</v>
       </c>
     </row>
     <row r="69">
@@ -2431,13 +2431,13 @@
         <v>46268</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>95879.81514593097</v>
+        <v>95656.96763874101</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>-0.005951799926913859</v>
+        <v>-0.006001839002291898</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>-0.04120184854069031</v>
+        <v>-0.04343032361258992</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>13932.5</v>
@@ -2446,7 +2446,7 @@
         <v>0.01667396380618791</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-0.05787581234687822</v>
+        <v>-0.06010428741877782</v>
       </c>
     </row>
     <row r="70">
@@ -2454,13 +2454,13 @@
         <v>46269</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>96958.88260276217</v>
+        <v>96734.41571162862</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.01125437564923182</v>
+        <v>0.01126366536054868</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.03041117397237825</v>
+        <v>-0.03265584288371381</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>14012.400390625</v>
@@ -2469,7 +2469,7 @@
         <v>0.02250440678816412</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.05291558076054237</v>
+        <v>-0.05516024967187794</v>
       </c>
     </row>
     <row r="71">
@@ -2477,13 +2477,13 @@
         <v>46272</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>96958.88260276217</v>
+        <v>96734.41571162862</v>
       </c>
       <c r="C71" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>-0.03041117397237825</v>
+        <v>-0.03265584288371381</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>14151.599609375</v>
@@ -2492,7 +2492,7 @@
         <v>0.03266196799292187</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-0.06307314196530012</v>
+        <v>-0.06531781087663568</v>
       </c>
     </row>
     <row r="72">
@@ -2500,13 +2500,13 @@
         <v>46273</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>104589.7615736458</v>
+        <v>104362.7299729162</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.07870221650704323</v>
+        <v>0.07885832777476098</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0.04589761573645745</v>
+        <v>0.04362729972916224</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>14405.2998046875</v>
@@ -2515,7 +2515,7 @@
         <v>0.05117482521070493</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.00527720947424748</v>
+        <v>-0.007547525481542694</v>
       </c>
     </row>
     <row r="73">
@@ -2523,13 +2523,13 @@
         <v>46274</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>103814.9758879968</v>
+        <v>103584.1657247322</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>-0.007407854019280569</v>
+        <v>-0.007460175183094941</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>0.03814975887996819</v>
+        <v>0.03584165724732236</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>14505.5</v>
@@ -2538,7 +2538,7 @@
         <v>0.05848657326328088</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>-0.0203368143833127</v>
+        <v>-0.02264491601595853</v>
       </c>
     </row>
     <row r="74">
@@ -2546,13 +2546,13 @@
         <v>46275</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>103370.0275112978</v>
+        <v>103137.8664913764</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>-0.004285974859533193</v>
+        <v>-0.004308566181262186</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0.03370027511297824</v>
+        <v>0.03137866491376395</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>14393.900390625</v>
@@ -2561,7 +2561,7 @@
         <v>0.05034299406195264</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.0166427189489744</v>
+        <v>-0.01896432914818869</v>
       </c>
     </row>
     <row r="75">
@@ -2569,13 +2569,13 @@
         <v>46276</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>104820.5075900477</v>
+        <v>104585.7818605303</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.01403192118325958</v>
+        <v>0.01403863991383814</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>0.04820507590047729</v>
+        <v>0.04585781860530336</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>14467.2998046875</v>
@@ -2584,7 +2584,7 @@
         <v>0.05569905171391554</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>-0.007493975813438247</v>
+        <v>-0.00984123310861218</v>
       </c>
     </row>
     <row r="76">
@@ -2592,13 +2592,13 @@
         <v>46279</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>102851.9766459601</v>
+        <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01878001728236767</v>
+        <v>-0.01879633345759624</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02851976645960086</v>
+        <v>0.02619952629756384</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01028640726248753</v>
+        <v>-0.01260664742452455</v>
       </c>
     </row>
     <row r="77">
@@ -2615,13 +2615,13 @@
         <v>46280</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>102851.9766459601</v>
+        <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0</v>
+        <v>-0.02504358406702301</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>0.02851976645960086</v>
+        <v>0.000499812191191662</v>
       </c>
       <c r="E77" s="5" t="n">
         <v>13892.2998046875</v>
@@ -2630,11 +2630,34 @@
         <v>0.01374049946639677</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0.01477926699320409</v>
+        <v>-0.01324068727520511</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>100049.9812191192</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0.000499812191191662</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>13122.599609375</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>-0.04242559768133392</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.04292540987252558</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G77"/>
+  <autoFilter ref="A1:G78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>BELOW_MA200_DEFENSIVE</t>
+          <t>ABOVE_MA200_RISK_ON</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13122.599609375</v>
+        <v>13509.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.000499812191191662</v>
+        <v>-0.06608137047768192</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.04242559768133392</v>
+        <v>-0.01417105920260509</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04292540987252558</v>
+        <v>-0.05191031127507684</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Üstü</t>
+          <t>Zararda / BIST Altı</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.2599983215332</v>
+        <v>34.77999877929688</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0435000419616699</v>
+        <v>-0.1305000305175781</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31883.331934611</v>
+        <v>28983.33231608073</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1450.001398722328</v>
+        <v>-4350.001017252602</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.40000152587891</v>
+        <v>38.22000122070312</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.06813183459606797</v>
+        <v>-0.1599999731713599</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>31062.27218013106</v>
+        <v>28000.000894288</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-2271.061153202267</v>
+        <v>-5333.332439045331</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>413.25</v>
+        <v>405.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1131313131313132</v>
+        <v>0.09225589225589226</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37104.3771043771</v>
+        <v>36408.52974186307</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3771.043771043769</v>
+        <v>3075.196408529744</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2638,13 +2638,13 @@
         <v>46281</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>100049.9812191192</v>
+        <v>93391.86295223179</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0</v>
+        <v>-0.06654792120655617</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.000499812191191662</v>
+        <v>-0.06608137047768203</v>
       </c>
       <c r="E78" s="5" t="n">
         <v>13122.599609375</v>
@@ -2653,11 +2653,34 @@
         <v>-0.04242559768133392</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.04292540987252558</v>
+        <v>-0.02365577279634812</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>93391.86295223179</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-0.06608137047768203</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>13509.7998046875</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>-0.01417105920260509</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-0.05191031127507695</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G78"/>
+  <autoFilter ref="A1:G79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,7 +535,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ABOVE_MA200_RISK_ON</t>
+          <t>BELOW_MA200_DEFENSIVE</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13509.7998046875</v>
+        <v>13284.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.01417105920260509</v>
+        <v>-0.03061876892695559</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.05191031127507684</v>
+        <v>-0.03546260155072634</v>
       </c>
     </row>
     <row r="19">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2477,13 +2477,13 @@
         <v>46272</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>96734.41571162862</v>
+        <v>99758.66294083888</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0</v>
+        <v>0.03126340513830916</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>-0.03265584288371381</v>
+        <v>-0.002413370591611175</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>14151.599609375</v>
@@ -2492,7 +2492,7 @@
         <v>0.03266196799292187</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-0.06531781087663568</v>
+        <v>-0.03507533858453304</v>
       </c>
     </row>
     <row r="72">
@@ -2503,7 +2503,7 @@
         <v>104362.7299729162</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.07885832777476098</v>
+        <v>0.04615205232660102</v>
       </c>
       <c r="D72" s="4" t="n">
         <v>0.04362729972916224</v>
@@ -2679,8 +2679,31 @@
         <v>-0.05191031127507695</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>93391.86295223179</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-0.06608137047768203</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>13284.400390625</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>-0.03061876892695559</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-0.03546260155072645</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G79"/>
+  <autoFilter ref="A1:G80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -916,10 +916,10 @@
         <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602344735420602</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608915285652106</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573839</v>
+        <v>-0.01516627338573817</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751684</v>
+        <v>0.01458616347751707</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955845</v>
+        <v>-0.06061085928955823</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008213118147898379</v>
+        <v>-0.00082131181479006</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551964</v>
+        <v>99701.94672551962</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621612</v>
+        <v>-0.007073005927621834</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.002980532744803588</v>
+        <v>-0.00298053274480381</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04874820607467067</v>
+        <v>-0.0487482060746709</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00180034251077299</v>
+        <v>-0.001800342510772768</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409486</v>
+        <v>-0.01334406573409508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00366991614864931</v>
+        <v>0.003669916148649088</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968264</v>
+        <v>-0.03129799068968286</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180841</v>
+        <v>-0.01576249680180819</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425054</v>
+        <v>99094.94601425053</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.009050539857494599</v>
+        <v>-0.00905053985749471</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0562338154978187</v>
+        <v>-0.05623381549781881</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.00593839502983573</v>
+        <v>-0.005938395029835619</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956823</v>
+        <v>97308.67800956822</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614126</v>
+        <v>-0.02106911747614149</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431761</v>
+        <v>-0.02691321990431783</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787283</v>
+        <v>-0.06237731797787305</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982734163</v>
+        <v>-0.004314514982733941</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866686</v>
+        <v>0.02121828779866664</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711579</v>
+        <v>0.01156806056711557</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300097</v>
+        <v>-0.01586918403300119</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820384</v>
+        <v>0.03846461342820406</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235539</v>
+        <v>0.02467092015235517</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532714</v>
+        <v>0.04632805543532692</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0195475533921281</v>
+        <v>0.01954755339212788</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614189</v>
+        <v>-0.02556649570614167</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667342</v>
+        <v>95488.37939667344</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.04511620603326572</v>
+        <v>-0.0451162060332656</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361011</v>
+        <v>-0.07605607760361</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227376</v>
+        <v>97722.23537227378</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092787</v>
+        <v>-0.004717395579092676</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726242</v>
+        <v>-0.02277764627726231</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969083</v>
+        <v>-0.08097233395969072</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991624</v>
+        <v>98425.88257991623</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006374778211714838</v>
+        <v>-0.00637477821171506</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083754</v>
+        <v>-0.01574117420083776</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903374</v>
+        <v>-0.07933574512903396</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939357</v>
+        <v>0.007072410694939579</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347899</v>
+        <v>97531.90369347902</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446696</v>
+        <v>-0.01604171927446674</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306521006</v>
+        <v>-0.02468096306520984</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.07066021068451822</v>
+        <v>-0.070660210684518</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471233</v>
+        <v>96900.04456471234</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556386</v>
+        <v>-0.006478486575556497</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.03099955435287671</v>
+        <v>-0.0309995543528766</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974184</v>
+        <v>-0.06930953683974173</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006867825931805349</v>
+        <v>-0.00686782593180546</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759624</v>
+        <v>-0.01879633345759602</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756384</v>
+        <v>0.02619952629756406</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452455</v>
+        <v>-0.01260664742452433</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702301</v>
+        <v>-0.02504358406702312</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13284.400390625</v>
+        <v>13337.7001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.06608137047768192</v>
+        <v>-0.02936370261415544</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.03061876892695559</v>
+        <v>-0.02672940781432431</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.03546260155072634</v>
+        <v>-0.002634294799831127</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>34.77999877929688</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1305000305175781</v>
+        <v>-0.08950004577636717</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>28983.33231608073</v>
+        <v>30349.99847412109</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-4350.001017252602</v>
+        <v>-2983.334859212238</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.22000122070312</v>
+        <v>39.61999893188477</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1599999731713599</v>
+        <v>-0.1292307927058294</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28000.000894288</v>
+        <v>29025.64024313902</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5333.332439045331</v>
+        <v>-4307.693090194312</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>405.5</v>
+        <v>419.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09225589225589226</v>
+        <v>0.1306397306397307</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36408.52974186307</v>
+        <v>37687.99102132435</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3075.196408529744</v>
+        <v>4354.657687991021</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -916,10 +916,10 @@
         <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602344735420602</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652106</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573817</v>
+        <v>-0.01516627338573839</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751707</v>
+        <v>0.01458616347751684</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955823</v>
+        <v>-0.06061085928955845</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.00082131181479006</v>
+        <v>-0.0008213118147898379</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551962</v>
+        <v>99701.94672551964</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621834</v>
+        <v>-0.007073005927621612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.00298053274480381</v>
+        <v>-0.002980532744803588</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0487482060746709</v>
+        <v>-0.04874820607467067</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001800342510772768</v>
+        <v>-0.00180034251077299</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409508</v>
+        <v>-0.01334406573409486</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.003669916148649088</v>
+        <v>0.00366991614864931</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968286</v>
+        <v>-0.03129799068968264</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180819</v>
+        <v>-0.01576249680180841</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425053</v>
+        <v>99094.94601425054</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.00905053985749471</v>
+        <v>-0.009050539857494599</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05623381549781881</v>
+        <v>-0.0562338154978187</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005938395029835619</v>
+        <v>-0.00593839502983573</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956822</v>
+        <v>97308.67800956823</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614149</v>
+        <v>-0.02106911747614126</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431783</v>
+        <v>-0.02691321990431761</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787305</v>
+        <v>-0.06237731797787283</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982733941</v>
+        <v>-0.004314514982734163</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866664</v>
+        <v>0.02121828779866686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711557</v>
+        <v>0.01156806056711579</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300119</v>
+        <v>-0.01586918403300097</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820406</v>
+        <v>0.03846461342820384</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235517</v>
+        <v>0.02467092015235539</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532692</v>
+        <v>0.04632805543532714</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.01954755339212788</v>
+        <v>0.0195475533921281</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614167</v>
+        <v>-0.02556649570614189</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667344</v>
+        <v>95488.37939667342</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.0451162060332656</v>
+        <v>-0.04511620603326572</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361</v>
+        <v>-0.07605607760361011</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227378</v>
+        <v>97722.23537227376</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092676</v>
+        <v>-0.004717395579092787</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726231</v>
+        <v>-0.02277764627726242</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969072</v>
+        <v>-0.08097233395969083</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991623</v>
+        <v>98425.88257991624</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.00637477821171506</v>
+        <v>-0.006374778211714838</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083776</v>
+        <v>-0.01574117420083754</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903396</v>
+        <v>-0.07933574512903374</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939579</v>
+        <v>0.007072410694939357</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347902</v>
+        <v>97531.90369347899</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446674</v>
+        <v>-0.01604171927446696</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306520984</v>
+        <v>-0.02468096306521006</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.070660210684518</v>
+        <v>-0.07066021068451822</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471234</v>
+        <v>96900.04456471233</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556497</v>
+        <v>-0.006478486575556386</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.0309995543528766</v>
+        <v>-0.03099955435287671</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974173</v>
+        <v>-0.06930953683974184</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.00686782593180546</v>
+        <v>-0.006867825931805349</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759602</v>
+        <v>-0.01879633345759624</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756406</v>
+        <v>0.02619952629756384</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452433</v>
+        <v>-0.01260664742452455</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702312</v>
+        <v>-0.02504358406702301</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2661,13 +2661,13 @@
         <v>46282</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>93391.86295223179</v>
+        <v>97083.42801504066</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0</v>
+        <v>0.0395276948774117</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>-0.06608137047768203</v>
+        <v>-0.02916571984959337</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>13509.7998046875</v>
@@ -2676,7 +2676,7 @@
         <v>-0.01417105920260509</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>-0.05191031127507695</v>
+        <v>-0.01499466064698829</v>
       </c>
     </row>
     <row r="80">
@@ -2684,13 +2684,13 @@
         <v>46283</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>93391.86295223179</v>
+        <v>97063.62973858445</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0</v>
+        <v>-0.0002039305457275375</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.06608137047768203</v>
+        <v>-0.02936370261415544</v>
       </c>
       <c r="E80" s="5" t="n">
         <v>13284.400390625</v>
@@ -2699,11 +2699,34 @@
         <v>-0.03061876892695559</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.03546260155072645</v>
+        <v>0.001255066312800146</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>97063.62973858445</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>-0.02936370261415544</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>13337.7001953125</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>-0.02672940781432431</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>-0.002634294799831127</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G80"/>
+  <autoFilter ref="A1:G81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02936370261415544</v>
+        <v>-0.004045675506622048</v>
       </c>
     </row>
     <row r="17">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.002634294799831127</v>
+        <v>0.02268373230770226</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Zararda / BIST Altı</t>
+          <t>Zararda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.41999816894531</v>
+        <v>37.38000106811523</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08950004577636717</v>
+        <v>-0.0654999732971191</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30349.99847412109</v>
+        <v>31150.00089009602</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2983.334859212238</v>
+        <v>-2183.332443237305</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.61999893188477</v>
+        <v>40.36000061035156</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1292307927058294</v>
+        <v>-0.1129670195527129</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29025.64024313902</v>
+        <v>29567.76601490956</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4307.693090194312</v>
+        <v>-3765.567318423764</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>419.75</v>
+        <v>433</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1306397306397307</v>
+        <v>0.1663299663299664</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37687.99102132435</v>
+        <v>38877.66554433221</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4354.657687991021</v>
+        <v>5544.33221099888</v>
       </c>
     </row>
   </sheetData>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2707,13 +2707,13 @@
         <v>46286</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>97063.62973858445</v>
+        <v>99595.43244933782</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>0</v>
+        <v>0.0260839484116977</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>-0.02936370261415544</v>
+        <v>-0.004045675506621826</v>
       </c>
       <c r="E81" s="5" t="n">
         <v>13337.7001953125</v>
@@ -2722,7 +2722,7 @@
         <v>-0.02672940781432431</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>-0.002634294799831127</v>
+        <v>0.02268373230770249</v>
       </c>
     </row>
   </sheetData>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13337.7001953125</v>
+        <v>13251.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.004045675506622048</v>
+        <v>-0.003580773587017028</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.02672940781432431</v>
+        <v>-0.03299033927138062</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02268373230770226</v>
+        <v>0.02940956568436359</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.38000106811523</v>
+        <v>37.81999969482422</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0654999732971191</v>
+        <v>-0.05450000762939455</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31150.00089009602</v>
+        <v>31516.66641235351</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2183.332443237305</v>
+        <v>-1816.666920979816</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.36000061035156</v>
+        <v>40.2599983215332</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1129670195527129</v>
+        <v>-0.1151648720542153</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29567.76601490956</v>
+        <v>29494.50426485949</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3765.567318423764</v>
+        <v>-3838.829068473842</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>433</v>
+        <v>430.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1663299663299664</v>
+        <v>0.1589225589225589</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38877.66554433221</v>
+        <v>38630.75196408529</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5544.33221099888</v>
+        <v>5297.418630751963</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2725,8 +2725,54 @@
         <v>0.02268373230770249</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>99641.9226412983</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>0.0004667904021014024</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>-0.003580773587017028</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>13337.7001953125</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>-0.02672940781432431</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.02314863422730729</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>99641.9226412983</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>-0.003580773587017028</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>13251.900390625</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>-0.03299033927138062</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0.02940956568436359</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G81"/>
+  <autoFilter ref="A1:G83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13251.900390625</v>
+        <v>12888.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.003580773587017028</v>
+        <v>0.006587437562079801</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.03299033927138062</v>
+        <v>-0.05952278132753208</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02940956568436359</v>
+        <v>0.06611021888961188</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Zararda / BIST Üstü</t>
+          <t>Karda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.81999969482422</v>
+        <v>38.54000091552734</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05450000762939455</v>
+        <v>-0.03649997711181641</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31516.66641235351</v>
+        <v>32116.66742960611</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1816.666920979816</v>
+        <v>-1216.665903727215</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.2599983215332</v>
+        <v>40.40000152587891</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1151648720542153</v>
+        <v>-0.112087878552112</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29494.50426485949</v>
+        <v>29597.0707149296</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3838.829068473842</v>
+        <v>-3736.262618403733</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>430.25</v>
+        <v>433.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1589225589225589</v>
+        <v>0.1683501683501682</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38630.75196408529</v>
+        <v>38945.00561167227</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5297.418630751963</v>
+        <v>5611.672278338941</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2753,13 +2753,13 @@
         <v>46288</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>99641.9226412983</v>
+        <v>100658.743756208</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0</v>
+        <v>0.01020475205572002</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>-0.003580773587017028</v>
+        <v>0.006587437562079801</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>13251.900390625</v>
@@ -2768,11 +2768,34 @@
         <v>-0.03299033927138062</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>0.02940956568436359</v>
+        <v>0.03957777683346042</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>100658.743756208</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0.006587437562079801</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>12888.2998046875</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>-0.05952278132753208</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0.06611021888961188</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G83"/>
+  <autoFilter ref="A1:G84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12888.2998046875</v>
+        <v>12899.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.006587437562079801</v>
+        <v>-0.01751990960209227</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.05952278132753208</v>
+        <v>-0.05871275608399007</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.06611021888961188</v>
+        <v>0.0411928464818978</v>
       </c>
     </row>
     <row r="19">
@@ -669,7 +669,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Karda / BIST Üstü</t>
+          <t>Zararda / BIST Üstü</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>38.54000091552734</v>
+        <v>37.93999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.03649997711181641</v>
+        <v>-0.05150003433227535</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>32116.66742960611</v>
+        <v>31616.66552225748</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1216.665903727215</v>
+        <v>-1716.667811075844</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>40.40000152587891</v>
+        <v>39.13999938964844</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.112087878552112</v>
+        <v>-0.1397802331945398</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>29597.0707149296</v>
+        <v>28673.99222684867</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-3736.262618403733</v>
+        <v>-4659.341106484659</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>433.75</v>
+        <v>422.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1683501683501682</v>
+        <v>0.1387205387205388</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38945.00561167227</v>
+        <v>37957.35129068462</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5611.672278338941</v>
+        <v>4624.017957351294</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2739,13 +2739,13 @@
         <v>-0.003580773587017028</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>13337.7001953125</v>
+        <v>13198.7998046875</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.02672940781432431</v>
+        <v>-0.03686516311387189</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.02314863422730729</v>
+        <v>0.03328438952685486</v>
       </c>
     </row>
     <row r="83">
@@ -2776,13 +2776,13 @@
         <v>46289</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>100658.743756208</v>
+        <v>98248.00903979079</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0</v>
+        <v>-0.02394958079604004</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0.006587437562079801</v>
+        <v>-0.01751990960209215</v>
       </c>
       <c r="E84" s="5" t="n">
         <v>12888.2998046875</v>
@@ -2791,11 +2791,34 @@
         <v>-0.05952278132753208</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.06611021888961188</v>
+        <v>0.04200287172543993</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>98248.00903979079</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>-0.01751990960209215</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>12899.400390625</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>-0.05871275608399007</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0.04119284648189792</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G84"/>
+  <autoFilter ref="A1:G85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -756,7 +756,7 @@
         <v>37.93999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05150003433227535</v>
+        <v>-0.05150003433227557</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
@@ -765,7 +765,7 @@
         <v>31616.66552225748</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1716.667811075844</v>
+        <v>-1716.667811075851</v>
       </c>
     </row>
     <row r="3">
@@ -916,10 +916,10 @@
         <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602344735420602</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608915285652106</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573839</v>
+        <v>-0.01516627338573817</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751684</v>
+        <v>0.01458616347751707</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955845</v>
+        <v>-0.06061085928955823</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008213118147898379</v>
+        <v>-0.00082131181479006</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551964</v>
+        <v>99701.94672551962</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621612</v>
+        <v>-0.007073005927621834</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.002980532744803588</v>
+        <v>-0.00298053274480381</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04874820607467067</v>
+        <v>-0.0487482060746709</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00180034251077299</v>
+        <v>-0.001800342510772768</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409486</v>
+        <v>-0.01334406573409508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00366991614864931</v>
+        <v>0.003669916148649088</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968264</v>
+        <v>-0.03129799068968286</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180841</v>
+        <v>-0.01576249680180819</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425054</v>
+        <v>99094.94601425053</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.009050539857494599</v>
+        <v>-0.00905053985749471</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0562338154978187</v>
+        <v>-0.05623381549781881</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.00593839502983573</v>
+        <v>-0.005938395029835619</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956823</v>
+        <v>97308.67800956822</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614126</v>
+        <v>-0.02106911747614149</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431761</v>
+        <v>-0.02691321990431783</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787283</v>
+        <v>-0.06237731797787305</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982734163</v>
+        <v>-0.004314514982733941</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866686</v>
+        <v>0.02121828779866664</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711579</v>
+        <v>0.01156806056711557</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300097</v>
+        <v>-0.01586918403300119</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820384</v>
+        <v>0.03846461342820406</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235539</v>
+        <v>0.02467092015235517</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532714</v>
+        <v>0.04632805543532692</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0195475533921281</v>
+        <v>0.01954755339212788</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614189</v>
+        <v>-0.02556649570614167</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667342</v>
+        <v>95488.37939667344</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.04511620603326572</v>
+        <v>-0.0451162060332656</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361011</v>
+        <v>-0.07605607760361</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227376</v>
+        <v>97722.23537227378</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092787</v>
+        <v>-0.004717395579092676</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726242</v>
+        <v>-0.02277764627726231</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969083</v>
+        <v>-0.08097233395969072</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991624</v>
+        <v>98425.88257991623</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006374778211714838</v>
+        <v>-0.00637477821171506</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083754</v>
+        <v>-0.01574117420083776</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903374</v>
+        <v>-0.07933574512903396</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939357</v>
+        <v>0.007072410694939579</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347899</v>
+        <v>97531.90369347902</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446696</v>
+        <v>-0.01604171927446674</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306521006</v>
+        <v>-0.02468096306520984</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.07066021068451822</v>
+        <v>-0.070660210684518</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471233</v>
+        <v>96900.04456471234</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556386</v>
+        <v>-0.006478486575556497</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.03099955435287671</v>
+        <v>-0.0309995543528766</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974184</v>
+        <v>-0.06930953683974173</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006867825931805349</v>
+        <v>-0.00686782593180546</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759624</v>
+        <v>-0.01879633345759602</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756384</v>
+        <v>0.02619952629756406</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452455</v>
+        <v>-0.01260664742452433</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702301</v>
+        <v>-0.02504358406702312</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12899.400390625</v>
+        <v>12592.7998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01751990960209227</v>
+        <v>-0.01665819820787462</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.05871275608399007</v>
+        <v>-0.08108582861299618</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.0411928464818978</v>
+        <v>0.06442763040512156</v>
       </c>
     </row>
     <row r="19">
@@ -691,7 +691,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.93999862670898</v>
+        <v>37.7400016784668</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05150003433227557</v>
+        <v>-0.05649995803833008</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31616.66552225748</v>
+        <v>31450.00139872232</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1716.667811075851</v>
+        <v>-1883.331934611004</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.13999938964844</v>
+        <v>39.2400016784668</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1397802331945398</v>
+        <v>-0.1375823806930374</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28673.99222684867</v>
+        <v>28747.25397689875</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4659.341106484659</v>
+        <v>-4586.07935643458</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>422.75</v>
+        <v>424.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1387205387205388</v>
+        <v>0.1441077441077441</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37957.35129068462</v>
+        <v>38136.92480359146</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4624.017957351294</v>
+        <v>4803.591470258136</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -916,10 +916,10 @@
         <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602344735420602</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652106</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573817</v>
+        <v>-0.01516627338573839</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751707</v>
+        <v>0.01458616347751684</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955823</v>
+        <v>-0.06061085928955845</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.00082131181479006</v>
+        <v>-0.0008213118147898379</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551962</v>
+        <v>99701.94672551964</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621834</v>
+        <v>-0.007073005927621612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.00298053274480381</v>
+        <v>-0.002980532744803588</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0487482060746709</v>
+        <v>-0.04874820607467067</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001800342510772768</v>
+        <v>-0.00180034251077299</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409508</v>
+        <v>-0.01334406573409486</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.003669916148649088</v>
+        <v>0.00366991614864931</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968286</v>
+        <v>-0.03129799068968264</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180819</v>
+        <v>-0.01576249680180841</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425053</v>
+        <v>99094.94601425054</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.00905053985749471</v>
+        <v>-0.009050539857494599</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05623381549781881</v>
+        <v>-0.0562338154978187</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005938395029835619</v>
+        <v>-0.00593839502983573</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956822</v>
+        <v>97308.67800956823</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614149</v>
+        <v>-0.02106911747614126</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431783</v>
+        <v>-0.02691321990431761</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787305</v>
+        <v>-0.06237731797787283</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982733941</v>
+        <v>-0.004314514982734163</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866664</v>
+        <v>0.02121828779866686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711557</v>
+        <v>0.01156806056711579</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300119</v>
+        <v>-0.01586918403300097</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820406</v>
+        <v>0.03846461342820384</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235517</v>
+        <v>0.02467092015235539</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532692</v>
+        <v>0.04632805543532714</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.01954755339212788</v>
+        <v>0.0195475533921281</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614167</v>
+        <v>-0.02556649570614189</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667344</v>
+        <v>95488.37939667342</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.0451162060332656</v>
+        <v>-0.04511620603326572</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361</v>
+        <v>-0.07605607760361011</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227378</v>
+        <v>97722.23537227376</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092676</v>
+        <v>-0.004717395579092787</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726231</v>
+        <v>-0.02277764627726242</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969072</v>
+        <v>-0.08097233395969083</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991623</v>
+        <v>98425.88257991624</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.00637477821171506</v>
+        <v>-0.006374778211714838</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083776</v>
+        <v>-0.01574117420083754</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903396</v>
+        <v>-0.07933574512903374</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939579</v>
+        <v>0.007072410694939357</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347902</v>
+        <v>97531.90369347899</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446674</v>
+        <v>-0.01604171927446696</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306520984</v>
+        <v>-0.02468096306521006</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.070660210684518</v>
+        <v>-0.07066021068451822</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471234</v>
+        <v>96900.04456471233</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556497</v>
+        <v>-0.006478486575556386</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.0309995543528766</v>
+        <v>-0.03099955435287671</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974173</v>
+        <v>-0.06930953683974184</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.00686782593180546</v>
+        <v>-0.006867825931805349</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759602</v>
+        <v>-0.01879633345759624</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756406</v>
+        <v>0.02619952629756384</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452433</v>
+        <v>-0.01260664742452455</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702312</v>
+        <v>-0.02504358406702301</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2799,13 +2799,13 @@
         <v>46290</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>98248.00903979079</v>
+        <v>98334.18017921255</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>0</v>
+        <v>0.0008770777165252319</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>-0.01751990960209215</v>
+        <v>-0.01665819820787451</v>
       </c>
       <c r="E85" s="5" t="n">
         <v>12899.400390625</v>
@@ -2814,11 +2814,34 @@
         <v>-0.05871275608399007</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.04119284648189792</v>
+        <v>0.04205455787611556</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>98334.18017921255</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>-0.01665819820787451</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>12592.7998046875</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>-0.08108582861299618</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0.06442763040512167</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85"/>
+  <autoFilter ref="A1:G86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12592.7998046875</v>
+        <v>12290.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.01665819820787462</v>
+        <v>-0.02355398521033336</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.08108582861299618</v>
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.06442763040512156</v>
+        <v>0.07958381328828024</v>
       </c>
     </row>
     <row r="19">
@@ -691,7 +691,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.7400016784668</v>
+        <v>37.47999954223633</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05649995803833008</v>
+        <v>-0.06300001144409184</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31450.00139872232</v>
+        <v>31233.3329518636</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1883.331934611004</v>
+        <v>-2100.000381469727</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>39.2400016784668</v>
+        <v>38.38000106811523</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1375823806930374</v>
+        <v>-0.1564834930084564</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28747.25397689875</v>
+        <v>28117.21689971811</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-4586.07935643458</v>
+        <v>-5216.116433615214</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>424.75</v>
+        <v>426.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1441077441077441</v>
+        <v>0.1488215488215487</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38136.92480359146</v>
+        <v>38294.05162738495</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4803.591470258136</v>
+        <v>4960.718294051621</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2822,13 +2822,13 @@
         <v>46293</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>98334.18017921255</v>
+        <v>97644.60147896668</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0</v>
+        <v>-0.007012604355770558</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.01665819820787451</v>
+        <v>-0.02355398521033325</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>12592.7998046875</v>
@@ -2837,11 +2837,34 @@
         <v>-0.08108582861299618</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.06442763040512167</v>
+        <v>0.05753184340266293</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>97644.60147896668</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>-0.02355398521033325</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>12290.599609375</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>-0.1031377984986136</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0.07958381328828035</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G86"/>
+  <autoFilter ref="A1:G87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12290.599609375</v>
+        <v>11947.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.02355398521033336</v>
+        <v>-0.03499102636869811</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1031377984986136</v>
+        <v>-0.1281961328581072</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.07958381328828024</v>
+        <v>0.09320510648940905</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.47999954223633</v>
+        <v>36.7599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06300001144409184</v>
+        <v>-0.08100004196166988</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31233.3329518636</v>
+        <v>30633.331934611</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2100.000381469727</v>
+        <v>-2700.001398722328</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.38000106811523</v>
+        <v>38.22000122070312</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1564834930084564</v>
+        <v>-0.1599999731713599</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28117.21689971811</v>
+        <v>28000.000894288</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5216.116433615214</v>
+        <v>-5333.332439045331</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>426.5</v>
+        <v>421.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1488215488215487</v>
+        <v>0.1360269360269359</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>38294.05162738495</v>
+        <v>37867.56453423119</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4960.718294051621</v>
+        <v>4534.231200897862</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2845,13 +2845,13 @@
         <v>46294</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>97644.60147896668</v>
+        <v>96500.89736313019</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0</v>
+        <v>-0.01171292727414985</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>-0.02355398521033325</v>
+        <v>-0.03499102636869811</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>12290.599609375</v>
@@ -2860,11 +2860,34 @@
         <v>-0.1031377984986136</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.07958381328828035</v>
+        <v>0.06814677212991549</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>96500.89736313019</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>-0.03499102636869811</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>11947.2001953125</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>-0.1281961328581072</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0.09320510648940905</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G87"/>
+  <autoFilter ref="A1:G88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11947.2001953125</v>
+        <v>12249</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.03499102636869811</v>
+        <v>-0.05587796123274735</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1281961328581072</v>
+        <v>-0.1061733800350263</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.09320510648940905</v>
+        <v>0.05029541880227895</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.7599983215332</v>
+        <v>35.93999862670898</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08100004196166988</v>
+        <v>-0.1015000343322754</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30633.331934611</v>
+        <v>29949.99885559082</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2700.001398722328</v>
+        <v>-3383.334477742512</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.22000122070312</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1599999731713599</v>
+        <v>-0.1934065766386933</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>28000.000894288</v>
+        <v>26886.44744537689</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5333.332439045331</v>
+        <v>-6446.885887956443</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>421.75</v>
+        <v>418.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1360269360269359</v>
+        <v>0.1272727272727272</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37867.56453423119</v>
+        <v>37575.75757575757</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4534.231200897862</v>
+        <v>4242.42424242424</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2868,13 +2868,13 @@
         <v>46295</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>96500.89736313019</v>
+        <v>94412.20387672528</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0</v>
+        <v>-0.02164429081467711</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.03499102636869811</v>
+        <v>-0.05587796123274713</v>
       </c>
       <c r="E88" s="5" t="n">
         <v>11947.2001953125</v>
@@ -2883,11 +2883,34 @@
         <v>-0.1281961328581072</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.09320510648940905</v>
+        <v>0.07231817162536003</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>94412.20387672528</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>-0.05587796123274713</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>12249</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>-0.1061733800350263</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0.05029541880227917</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G88"/>
+  <autoFilter ref="A1:G89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12249</v>
+        <v>12270.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.05587796123274735</v>
+        <v>-0.05495026123335378</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1061733800350263</v>
+        <v>-0.1046263722042834</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.05029541880227895</v>
+        <v>0.04967611097092961</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>35.93999862670898</v>
+        <v>36.61999893188477</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1015000343322754</v>
+        <v>-0.08450002670288081</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>29949.99885559082</v>
+        <v>30516.66577657064</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-3383.334477742512</v>
+        <v>-2816.667556762692</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.70000076293945</v>
+        <v>37.34000015258789</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1934065766386933</v>
+        <v>-0.1793406559870794</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>26886.44744537689</v>
+        <v>27355.31146709735</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-6446.885887956443</v>
+        <v>-5978.021866235977</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>418.5</v>
+        <v>408</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1272727272727272</v>
+        <v>0.09898989898989896</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37575.75757575757</v>
+        <v>36632.99663299663</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>4242.42424242424</v>
+        <v>3299.663299663298</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2891,13 +2891,13 @@
         <v>46296</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>94412.20387672528</v>
+        <v>94504.97387666462</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0</v>
+        <v>0.000982606020514698</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>-0.05587796123274713</v>
+        <v>-0.05495026123335378</v>
       </c>
       <c r="E89" s="5" t="n">
         <v>12249</v>
@@ -2906,11 +2906,34 @@
         <v>-0.1061733800350263</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>0.05029541880227917</v>
+        <v>0.05122311880167252</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>94504.97387666462</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>-0.05495026123335378</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>12270.2001953125</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>-0.1046263722042834</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0.04967611097092961</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G89"/>
+  <autoFilter ref="A1:G90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -916,10 +916,10 @@
         <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018500060349182</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018500060349182</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.01602341995346235</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.00660894196674866</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573839</v>
+        <v>-0.01516627338573817</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751684</v>
+        <v>0.01458616347751707</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955845</v>
+        <v>-0.06061085928955823</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008213118147898379</v>
+        <v>-0.00082131181479006</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551964</v>
+        <v>99701.94672551962</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621612</v>
+        <v>-0.007073005927621834</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.002980532744803588</v>
+        <v>-0.00298053274480381</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04874820607467067</v>
+        <v>-0.0487482060746709</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00180034251077299</v>
+        <v>-0.001800342510772768</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409486</v>
+        <v>-0.01334406573409508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00366991614864931</v>
+        <v>0.003669916148649088</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968264</v>
+        <v>-0.03129799068968286</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180841</v>
+        <v>-0.01576249680180819</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425054</v>
+        <v>99094.94601425053</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.009050539857494599</v>
+        <v>-0.00905053985749471</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0562338154978187</v>
+        <v>-0.05623381549781881</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.00593839502983573</v>
+        <v>-0.005938395029835619</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956823</v>
+        <v>97308.67800956822</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614126</v>
+        <v>-0.02106911747614149</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431761</v>
+        <v>-0.02691321990431783</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787283</v>
+        <v>-0.06237731797787305</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982734163</v>
+        <v>-0.004314514982733941</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866686</v>
+        <v>0.02121828779866664</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711579</v>
+        <v>0.01156806056711557</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300097</v>
+        <v>-0.01586918403300119</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820384</v>
+        <v>0.03846461342820406</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235539</v>
+        <v>0.02467092015235517</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532714</v>
+        <v>0.04632805543532692</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0195475533921281</v>
+        <v>0.01954755339212788</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614189</v>
+        <v>-0.02556649570614167</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667342</v>
+        <v>95488.37939667344</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.04511620603326572</v>
+        <v>-0.0451162060332656</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361011</v>
+        <v>-0.07605607760361</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227376</v>
+        <v>97722.23537227378</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092787</v>
+        <v>-0.004717395579092676</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726242</v>
+        <v>-0.02277764627726231</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969083</v>
+        <v>-0.08097233395969072</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991624</v>
+        <v>98425.88257991623</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006374778211714838</v>
+        <v>-0.00637477821171506</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083754</v>
+        <v>-0.01574117420083776</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903374</v>
+        <v>-0.07933574512903396</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939357</v>
+        <v>0.007072410694939579</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347899</v>
+        <v>97531.90369347902</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446696</v>
+        <v>-0.01604171927446674</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306521006</v>
+        <v>-0.02468096306520984</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.07066021068451822</v>
+        <v>-0.070660210684518</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471233</v>
+        <v>96900.04456471234</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556386</v>
+        <v>-0.006478486575556497</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.03099955435287671</v>
+        <v>-0.0309995543528766</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974184</v>
+        <v>-0.06930953683974173</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006867825931805349</v>
+        <v>-0.00686782593180546</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759624</v>
+        <v>-0.01879633345759602</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756384</v>
+        <v>0.02619952629756406</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452455</v>
+        <v>-0.01260664742452433</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702301</v>
+        <v>-0.02504358406702312</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12270.2001953125</v>
+        <v>12443.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.05495026123335378</v>
+        <v>-0.04710882285125839</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1046263722042834</v>
+        <v>-0.09195122660354638</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04967611097092961</v>
+        <v>0.04484240375228798</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.61999893188477</v>
+        <v>37.02000045776367</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08450002670288081</v>
+        <v>-0.07449998855590823</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30516.66577657064</v>
+        <v>30850.00038146972</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2816.667556762692</v>
+        <v>-2483.332951863606</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.34000015258789</v>
+        <v>37.22000122070312</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1793406559870794</v>
+        <v>-0.1819779951493818</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27355.31146709735</v>
+        <v>27267.40016168727</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5978.021866235977</v>
+        <v>-6065.933171646062</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09898989898989896</v>
+        <v>0.1151515151515152</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36632.99663299663</v>
+        <v>37171.71717171717</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3299.663299663298</v>
+        <v>3838.383838383837</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -916,10 +916,10 @@
         <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349182</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349182</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346235</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.00660894196674866</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573817</v>
+        <v>-0.01516627338573839</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751707</v>
+        <v>0.01458616347751684</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955823</v>
+        <v>-0.06061085928955845</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.00082131181479006</v>
+        <v>-0.0008213118147898379</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551962</v>
+        <v>99701.94672551964</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621834</v>
+        <v>-0.007073005927621612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.00298053274480381</v>
+        <v>-0.002980532744803588</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0487482060746709</v>
+        <v>-0.04874820607467067</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001800342510772768</v>
+        <v>-0.00180034251077299</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409508</v>
+        <v>-0.01334406573409486</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.003669916148649088</v>
+        <v>0.00366991614864931</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968286</v>
+        <v>-0.03129799068968264</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180819</v>
+        <v>-0.01576249680180841</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425053</v>
+        <v>99094.94601425054</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.00905053985749471</v>
+        <v>-0.009050539857494599</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05623381549781881</v>
+        <v>-0.0562338154978187</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005938395029835619</v>
+        <v>-0.00593839502983573</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956822</v>
+        <v>97308.67800956823</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614149</v>
+        <v>-0.02106911747614126</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431783</v>
+        <v>-0.02691321990431761</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787305</v>
+        <v>-0.06237731797787283</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982733941</v>
+        <v>-0.004314514982734163</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866664</v>
+        <v>0.02121828779866686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711557</v>
+        <v>0.01156806056711579</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300119</v>
+        <v>-0.01586918403300097</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820406</v>
+        <v>0.03846461342820384</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235517</v>
+        <v>0.02467092015235539</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532692</v>
+        <v>0.04632805543532714</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.01954755339212788</v>
+        <v>0.0195475533921281</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614167</v>
+        <v>-0.02556649570614189</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667344</v>
+        <v>95488.37939667342</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.0451162060332656</v>
+        <v>-0.04511620603326572</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361</v>
+        <v>-0.07605607760361011</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227378</v>
+        <v>97722.23537227376</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092676</v>
+        <v>-0.004717395579092787</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726231</v>
+        <v>-0.02277764627726242</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969072</v>
+        <v>-0.08097233395969083</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991623</v>
+        <v>98425.88257991624</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.00637477821171506</v>
+        <v>-0.006374778211714838</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083776</v>
+        <v>-0.01574117420083754</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903396</v>
+        <v>-0.07933574512903374</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939579</v>
+        <v>0.007072410694939357</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347902</v>
+        <v>97531.90369347899</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446674</v>
+        <v>-0.01604171927446696</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306520984</v>
+        <v>-0.02468096306521006</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.070660210684518</v>
+        <v>-0.07066021068451822</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471234</v>
+        <v>96900.04456471233</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556497</v>
+        <v>-0.006478486575556386</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.0309995543528766</v>
+        <v>-0.03099955435287671</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974173</v>
+        <v>-0.06930953683974184</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.00686782593180546</v>
+        <v>-0.006867825931805349</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759602</v>
+        <v>-0.01879633345759624</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756406</v>
+        <v>0.02619952629756384</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452433</v>
+        <v>-0.01260664742452455</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702312</v>
+        <v>-0.02504358406702301</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2914,13 +2914,13 @@
         <v>46297</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>94504.97387666462</v>
+        <v>95289.11771487416</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0</v>
+        <v>0.008297381672555115</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.05495026123335378</v>
+        <v>-0.04710882285125839</v>
       </c>
       <c r="E90" s="5" t="n">
         <v>12270.2001953125</v>
@@ -2929,11 +2929,34 @@
         <v>-0.1046263722042834</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.04967611097092961</v>
+        <v>0.057517549353025</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>95289.11771487416</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>-0.04710882285125839</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>12443.900390625</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>-0.09195122660354638</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0.04484240375228798</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G90"/>
+  <autoFilter ref="A1:G91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12443.900390625</v>
+        <v>12374.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04710882285125839</v>
+        <v>-0.03594423254241297</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.09195122660354638</v>
+        <v>-0.09703007846705336</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04484240375228798</v>
+        <v>0.06108584592464039</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.02000045776367</v>
+        <v>37.63999938964844</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.07449998855590823</v>
+        <v>-0.05900001525878906</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30850.00038146972</v>
+        <v>31366.66615804036</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2483.332951863606</v>
+        <v>-1966.667175292969</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.22000122070312</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1819779951493818</v>
+        <v>-0.1626373961731628</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27267.40016168727</v>
+        <v>27912.0867942279</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-6065.933171646062</v>
+        <v>-5421.246539105425</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>414</v>
+        <v>413.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1151515151515152</v>
+        <v>0.1138047138047138</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37171.71717171717</v>
+        <v>37126.82379349045</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3838.383838383837</v>
+        <v>3793.490460157125</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2937,13 +2937,13 @@
         <v>46300</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>95289.11771487416</v>
+        <v>96405.57674575874</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0</v>
+        <v>0.01171654285041512</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>-0.04710882285125839</v>
+        <v>-0.03594423254241264</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>12443.900390625</v>
@@ -2952,11 +2952,34 @@
         <v>-0.09195122660354638</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.04484240375228798</v>
+        <v>0.05600699406113374</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>96405.57674575874</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>-0.03594423254241264</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>12374.2998046875</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>-0.09703007846705336</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0.06108584592464072</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G91"/>
+  <autoFilter ref="A1:G92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12374.2998046875</v>
+        <v>12122.900390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.03594423254241297</v>
+        <v>-0.04515940556729847</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.09703007846705336</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.06108584592464039</v>
+        <v>0.07021563889964544</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.63999938964844</v>
+        <v>37.08000183105469</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05900001525878906</v>
+        <v>-0.07299995422363281</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31366.66615804036</v>
+        <v>30900.0015258789</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-1966.667175292969</v>
+        <v>-2433.331807454426</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.09999847412109</v>
+        <v>38</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1626373961731628</v>
+        <v>-0.1648351648351648</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27912.0867942279</v>
+        <v>27838.82783882783</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5421.246539105425</v>
+        <v>-5494.505494505494</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>413.5</v>
+        <v>409.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1138047138047138</v>
+        <v>0.1023569023569024</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>37126.82379349045</v>
+        <v>36745.23007856341</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3793.490460157125</v>
+        <v>3411.896745230079</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -2960,13 +2960,13 @@
         <v>46301</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>96405.57674575874</v>
+        <v>95484.05944327016</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0</v>
+        <v>-0.009558755142545339</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.03594423254241264</v>
+        <v>-0.04515940556729836</v>
       </c>
       <c r="E92" s="5" t="n">
         <v>12374.2998046875</v>
@@ -2975,11 +2975,34 @@
         <v>-0.09703007846705336</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.06108584592464072</v>
+        <v>0.051870672899755</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>95484.05944327016</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>-0.04515940556729836</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>12122.900390625</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>-0.1153750444669439</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0.07021563889964555</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G92"/>
+  <autoFilter ref="A1:G93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12122.900390625</v>
+        <v>12213.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04515940556729847</v>
+        <v>-0.06651753030877372</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1153750444669439</v>
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.07021563889964544</v>
+        <v>0.04223906562124669</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.08000183105469</v>
+        <v>36.52000045776367</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.07299995422363281</v>
+        <v>-0.08699998855590818</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30900.0015258789</v>
+        <v>30433.33371480306</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2433.331807454426</v>
+        <v>-2899.999618530273</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38</v>
+        <v>37.56000137329102</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1648351648351648</v>
+        <v>-0.1745054643232744</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27838.82783882783</v>
+        <v>27516.48452255752</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5494.505494505494</v>
+        <v>-5816.848810775813</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>409.25</v>
+        <v>394.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1023569023569024</v>
+        <v>0.06195286195286198</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36745.23007856341</v>
+        <v>35398.42873176206</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3411.896745230079</v>
+        <v>2065.095398428733</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2983,13 +2983,13 @@
         <v>46302</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>95484.05944327016</v>
+        <v>93348.24696912264</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0</v>
+        <v>-0.02236826216439269</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>-0.04515940556729836</v>
+        <v>-0.06651753030877361</v>
       </c>
       <c r="E93" s="5" t="n">
         <v>12122.900390625</v>
@@ -2998,11 +2998,34 @@
         <v>-0.1153750444669439</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0.07021563889964555</v>
+        <v>0.0488575141581703</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>93348.24696912264</v>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>-0.06651753030877361</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>12213.599609375</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>-0.1087565959300204</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0.0422390656212468</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G93"/>
+  <autoFilter ref="A1:G94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12213.599609375</v>
+        <v>12266</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.06651753030877372</v>
+        <v>-0.057885524503554</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.104932866316404</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04223906562124669</v>
+        <v>0.04704734181284997</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.52000045776367</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08699998855590818</v>
+        <v>-0.08500003814697266</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30433.33371480306</v>
+        <v>30499.99872843424</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2899.999618530273</v>
+        <v>-2833.33460489909</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.56000137329102</v>
+        <v>37.81999969482422</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1745054643232744</v>
+        <v>-0.1687912154983688</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27516.48452255752</v>
+        <v>27706.9594833877</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5816.848810775813</v>
+        <v>-5626.373849945627</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>394.25</v>
+        <v>401</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.06195286195286198</v>
+        <v>0.08013468013468006</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35398.42873176206</v>
+        <v>36004.48933782266</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2065.095398428733</v>
+        <v>2671.156004489334</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -3006,13 +3006,13 @@
         <v>46303</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>93348.24696912264</v>
+        <v>94211.44754964461</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0</v>
+        <v>0.009247100063994651</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.06651753030877361</v>
+        <v>-0.05788552450355389</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>12213.599609375</v>
@@ -3021,11 +3021,34 @@
         <v>-0.1087565959300204</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.0422390656212468</v>
+        <v>0.05087107142646652</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>94211.44754964461</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>-0.05788552450355389</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>12266</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>-0.104932866316404</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>0.04704734181285009</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G94"/>
+  <autoFilter ref="A1:G95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -756,16 +756,16 @@
         <v>36.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08500003814697266</v>
+        <v>-0.08500003814697288</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30499.99872843424</v>
+        <v>30499.99872843423</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2833.33460489909</v>
+        <v>-2833.334604899097</v>
       </c>
     </row>
     <row r="3">
@@ -916,10 +916,10 @@
         <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602344735420602</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608915285652106</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573839</v>
+        <v>-0.01516627338573817</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751684</v>
+        <v>0.01458616347751707</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955845</v>
+        <v>-0.06061085928955823</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008213118147898379</v>
+        <v>-0.00082131181479006</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551964</v>
+        <v>99701.94672551962</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621612</v>
+        <v>-0.007073005927621834</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.002980532744803588</v>
+        <v>-0.00298053274480381</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04874820607467067</v>
+        <v>-0.0487482060746709</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00180034251077299</v>
+        <v>-0.001800342510772768</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409486</v>
+        <v>-0.01334406573409508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00366991614864931</v>
+        <v>0.003669916148649088</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968264</v>
+        <v>-0.03129799068968286</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180841</v>
+        <v>-0.01576249680180819</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425054</v>
+        <v>99094.94601425053</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.009050539857494599</v>
+        <v>-0.00905053985749471</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0562338154978187</v>
+        <v>-0.05623381549781881</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.00593839502983573</v>
+        <v>-0.005938395029835619</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956823</v>
+        <v>97308.67800956822</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614126</v>
+        <v>-0.02106911747614149</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431761</v>
+        <v>-0.02691321990431783</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787283</v>
+        <v>-0.06237731797787305</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982734163</v>
+        <v>-0.004314514982733941</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866686</v>
+        <v>0.02121828779866664</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711579</v>
+        <v>0.01156806056711557</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300097</v>
+        <v>-0.01586918403300119</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820384</v>
+        <v>0.03846461342820406</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235539</v>
+        <v>0.02467092015235517</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532714</v>
+        <v>0.04632805543532692</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0195475533921281</v>
+        <v>0.01954755339212788</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614189</v>
+        <v>-0.02556649570614167</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667342</v>
+        <v>95488.37939667344</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.04511620603326572</v>
+        <v>-0.0451162060332656</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361011</v>
+        <v>-0.07605607760361</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227376</v>
+        <v>97722.23537227378</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092787</v>
+        <v>-0.004717395579092676</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726242</v>
+        <v>-0.02277764627726231</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969083</v>
+        <v>-0.08097233395969072</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991624</v>
+        <v>98425.88257991623</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006374778211714838</v>
+        <v>-0.00637477821171506</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083754</v>
+        <v>-0.01574117420083776</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903374</v>
+        <v>-0.07933574512903396</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939357</v>
+        <v>0.007072410694939579</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347899</v>
+        <v>97531.90369347902</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446696</v>
+        <v>-0.01604171927446674</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306521006</v>
+        <v>-0.02468096306520984</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.07066021068451822</v>
+        <v>-0.070660210684518</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471233</v>
+        <v>96900.04456471234</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556386</v>
+        <v>-0.006478486575556497</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.03099955435287671</v>
+        <v>-0.0309995543528766</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974184</v>
+        <v>-0.06930953683974173</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006867825931805349</v>
+        <v>-0.00686782593180546</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759624</v>
+        <v>-0.01879633345759602</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756384</v>
+        <v>0.02619952629756406</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452455</v>
+        <v>-0.01260664742452433</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702301</v>
+        <v>-0.02504358406702312</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2937,13 +2937,13 @@
         <v>46300</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>96405.57674575874</v>
+        <v>96405.57674575872</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.01171654285041512</v>
+        <v>0.0117165428504149</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>-0.03594423254241264</v>
+        <v>-0.03594423254241286</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>12443.900390625</v>
@@ -2952,7 +2952,7 @@
         <v>-0.09195122660354638</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.05600699406113374</v>
+        <v>0.05600699406113352</v>
       </c>
     </row>
     <row r="92">
@@ -2963,7 +2963,7 @@
         <v>95484.05944327016</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.009558755142545339</v>
+        <v>-0.009558755142545117</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>-0.04515940556729836</v>
@@ -3006,13 +3006,13 @@
         <v>46303</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>94211.44754964461</v>
+        <v>94211.4475496446</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>0.009247100063994651</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.05788552450355389</v>
+        <v>-0.057885524503554</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>12213.599609375</v>
@@ -3021,7 +3021,7 @@
         <v>-0.1087565959300204</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.05087107142646652</v>
+        <v>0.05087107142646641</v>
       </c>
     </row>
     <row r="95">
@@ -3029,13 +3029,13 @@
         <v>46304</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>94211.44754964461</v>
+        <v>94211.4475496446</v>
       </c>
       <c r="C95" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>-0.05788552450355389</v>
+        <v>-0.057885524503554</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>12266</v>
@@ -3044,7 +3044,7 @@
         <v>-0.104932866316404</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.04704734181285009</v>
+        <v>0.04704734181284997</v>
       </c>
     </row>
   </sheetData>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12266</v>
+        <v>12150.7001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.057885524503554</v>
+        <v>-0.04870251553849125</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.104932866316404</v>
+        <v>-0.1133464539322461</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.04704734181284997</v>
+        <v>0.06464393839375482</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.59999847412109</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08500003814697288</v>
+        <v>-0.06700000762939451</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30499.99872843423</v>
+        <v>31099.99974568684</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2833.334604899097</v>
+        <v>-2233.333587646484</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.81999969482422</v>
+        <v>38.04000091552734</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1687912154983688</v>
+        <v>-0.1639560238345639</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27706.9594833877</v>
+        <v>27868.13253884787</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5626.373849945627</v>
+        <v>-5465.200794485463</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>401</v>
+        <v>402.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.08013468013468006</v>
+        <v>0.08484848484848495</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36004.48933782266</v>
+        <v>36161.61616161616</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2671.156004489334</v>
+        <v>2828.282828282834</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602344735420602</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652106</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573817</v>
+        <v>-0.01516627338573839</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751707</v>
+        <v>0.01458616347751684</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955823</v>
+        <v>-0.06061085928955845</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.00082131181479006</v>
+        <v>-0.0008213118147898379</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551962</v>
+        <v>99701.94672551964</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621834</v>
+        <v>-0.007073005927621612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.00298053274480381</v>
+        <v>-0.002980532744803588</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0487482060746709</v>
+        <v>-0.04874820607467067</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001800342510772768</v>
+        <v>-0.00180034251077299</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409508</v>
+        <v>-0.01334406573409486</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.003669916148649088</v>
+        <v>0.00366991614864931</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968286</v>
+        <v>-0.03129799068968264</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180819</v>
+        <v>-0.01576249680180841</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425053</v>
+        <v>99094.94601425054</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.00905053985749471</v>
+        <v>-0.009050539857494599</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05623381549781881</v>
+        <v>-0.0562338154978187</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005938395029835619</v>
+        <v>-0.00593839502983573</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956822</v>
+        <v>97308.67800956823</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614149</v>
+        <v>-0.02106911747614126</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431783</v>
+        <v>-0.02691321990431761</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787305</v>
+        <v>-0.06237731797787283</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982733941</v>
+        <v>-0.004314514982734163</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866664</v>
+        <v>0.02121828779866686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711557</v>
+        <v>0.01156806056711579</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300119</v>
+        <v>-0.01586918403300097</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820406</v>
+        <v>0.03846461342820384</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235517</v>
+        <v>0.02467092015235539</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532692</v>
+        <v>0.04632805543532714</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.01954755339212788</v>
+        <v>0.0195475533921281</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614167</v>
+        <v>-0.02556649570614189</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667344</v>
+        <v>95488.37939667342</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.0451162060332656</v>
+        <v>-0.04511620603326572</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361</v>
+        <v>-0.07605607760361011</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227378</v>
+        <v>97722.23537227376</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092676</v>
+        <v>-0.004717395579092787</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726231</v>
+        <v>-0.02277764627726242</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969072</v>
+        <v>-0.08097233395969083</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991623</v>
+        <v>98425.88257991624</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.00637477821171506</v>
+        <v>-0.006374778211714838</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083776</v>
+        <v>-0.01574117420083754</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903396</v>
+        <v>-0.07933574512903374</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939579</v>
+        <v>0.007072410694939357</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347902</v>
+        <v>97531.90369347899</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446674</v>
+        <v>-0.01604171927446696</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306520984</v>
+        <v>-0.02468096306521006</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.070660210684518</v>
+        <v>-0.07066021068451822</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471234</v>
+        <v>96900.04456471233</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556497</v>
+        <v>-0.006478486575556386</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.0309995543528766</v>
+        <v>-0.03099955435287671</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974173</v>
+        <v>-0.06930953683974184</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.00686782593180546</v>
+        <v>-0.006867825931805349</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759602</v>
+        <v>-0.01879633345759624</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756406</v>
+        <v>0.02619952629756384</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452433</v>
+        <v>-0.01260664742452455</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702312</v>
+        <v>-0.02504358406702301</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2937,13 +2937,13 @@
         <v>46300</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>96405.57674575872</v>
+        <v>96405.57674575874</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.0117165428504149</v>
+        <v>0.01171654285041512</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>-0.03594423254241286</v>
+        <v>-0.03594423254241264</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>12443.900390625</v>
@@ -2952,7 +2952,7 @@
         <v>-0.09195122660354638</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.05600699406113352</v>
+        <v>0.05600699406113374</v>
       </c>
     </row>
     <row r="92">
@@ -2963,7 +2963,7 @@
         <v>95484.05944327016</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.009558755142545117</v>
+        <v>-0.009558755142545339</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>-0.04515940556729836</v>
@@ -3006,13 +3006,13 @@
         <v>46303</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>94211.4475496446</v>
+        <v>94211.44754964461</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>0.009247100063994651</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.057885524503554</v>
+        <v>-0.05788552450355389</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>12213.599609375</v>
@@ -3021,7 +3021,7 @@
         <v>-0.1087565959300204</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.05087107142646641</v>
+        <v>0.05087107142646652</v>
       </c>
     </row>
     <row r="95">
@@ -3029,13 +3029,13 @@
         <v>46304</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>94211.4475496446</v>
+        <v>95129.74844615087</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0</v>
+        <v>0.009747232638818826</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>-0.057885524503554</v>
+        <v>-0.04870251553849125</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>12266</v>
@@ -3044,11 +3044,34 @@
         <v>-0.104932866316404</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.04704734181284997</v>
+        <v>0.05623035077791272</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>95129.74844615087</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>-0.04870251553849125</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>12150.7001953125</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>-0.1133464539322461</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0.06464393839375482</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G95"/>
+  <autoFilter ref="A1:G96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12150.7001953125</v>
+        <v>12250.7001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04870251553849125</v>
+        <v>-0.05520432576522627</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1133464539322461</v>
+        <v>-0.1060493144109385</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.06464393839375482</v>
+        <v>0.05084498864571219</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.31999969482422</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06700000762939451</v>
+        <v>-0.06000003814697263</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31099.99974568684</v>
+        <v>31333.33206176757</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2233.333587646484</v>
+        <v>-2000.001271565754</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>38.04000091552734</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1639560238345639</v>
+        <v>-0.1736264071621738</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27868.13253884787</v>
+        <v>27545.78642792753</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5465.200794485463</v>
+        <v>-5787.546905405794</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>402.75</v>
+        <v>396.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.08484848484848495</v>
+        <v>0.06801346801346808</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36161.61616161616</v>
+        <v>35600.44893378227</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2828.282828282834</v>
+        <v>2267.115600448938</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3052,13 +3052,13 @@
         <v>46307</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>95129.74844615087</v>
+        <v>94479.56742347739</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0</v>
+        <v>-0.006834676148035124</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.04870251553849125</v>
+        <v>-0.05520432576522616</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>12150.7001953125</v>
@@ -3067,11 +3067,34 @@
         <v>-0.1133464539322461</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.06464393839375482</v>
+        <v>0.05814212816701991</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>94479.56742347739</v>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>-0.05520432576522616</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>12250.7001953125</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>-0.1060493144109385</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0.0508449886457123</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G96"/>
+  <autoFilter ref="A1:G97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12250.7001953125</v>
+        <v>12118.2998046875</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.05520432576522627</v>
+        <v>-0.04274281273834335</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1060493144109385</v>
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.05084498864571219</v>
+        <v>0.07296794290325759</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.59999847412109</v>
+        <v>37.2599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06000003814697263</v>
+        <v>-0.06850004196166992</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31333.33206176757</v>
+        <v>31049.99860127766</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2000.001271565754</v>
+        <v>-2283.334732055664</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.59999847412109</v>
+        <v>37.88000106811523</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1736264071621738</v>
+        <v>-0.1674725039974674</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27545.78642792753</v>
+        <v>27750.91653341775</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5787.546905405794</v>
+        <v>-5582.41679991558</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>396.5</v>
+        <v>411.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.06801346801346808</v>
+        <v>0.1077441077441077</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>35600.44893378227</v>
+        <v>36924.80359147025</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2267.115600448938</v>
+        <v>3591.47025813692</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3075,13 +3075,13 @@
         <v>46308</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>94479.56742347739</v>
+        <v>95725.71872616568</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0</v>
+        <v>0.01318963810558937</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>-0.05520432576522616</v>
+        <v>-0.04274281273834324</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>12250.7001953125</v>
@@ -3090,11 +3090,34 @@
         <v>-0.1060493144109385</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>0.0508449886457123</v>
+        <v>0.06330650167259522</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>95725.71872616568</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>-0.04274281273834324</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>12118.2998046875</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>-0.1157107556416009</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.0729679429032577</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G97"/>
+  <autoFilter ref="A1:G98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12118.2998046875</v>
+        <v>12070.2001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.04274281273834335</v>
+        <v>-0.05036419899415068</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.07296794290325759</v>
+        <v>0.06885645225274806</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.2599983215332</v>
+        <v>37.09999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06850004196166992</v>
+        <v>-0.0725000381469727</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31049.99860127766</v>
+        <v>30916.66539510091</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2283.334732055664</v>
+        <v>-2416.667938232422</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.88000106811523</v>
+        <v>37.41999816894531</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1674725039974674</v>
+        <v>-0.1775824578253777</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27750.91653341775</v>
+        <v>27413.91807248741</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5582.41679991558</v>
+        <v>-5919.415260845923</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>411.25</v>
+        <v>408</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1077441077441077</v>
+        <v>0.09898989898989896</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36924.80359147025</v>
+        <v>36632.99663299663</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3591.47025813692</v>
+        <v>3299.663299663298</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3098,13 +3098,13 @@
         <v>46309</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>95725.71872616568</v>
+        <v>94963.58010058495</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0</v>
+        <v>-0.00796169133773672</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.04274281273834324</v>
+        <v>-0.05036419899415057</v>
       </c>
       <c r="E98" s="5" t="n">
         <v>12118.2998046875</v>
@@ -3113,11 +3113,34 @@
         <v>-0.1157107556416009</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.0729679429032577</v>
+        <v>0.06534655664745037</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>94963.58010058495</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>-0.05036419899415057</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>12070.2001953125</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>-0.1192206512468987</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0.06885645225274817</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G98"/>
+  <autoFilter ref="A1:G99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12070.2001953125</v>
+        <v>11721.7001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.05036419899415068</v>
+        <v>-0.05487247278660912</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1192206512468987</v>
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.06885645225274806</v>
+        <v>0.08977870969204671</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.09999847412109</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0725000381469727</v>
+        <v>-0.06499996185302737</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30916.66539510091</v>
+        <v>31166.66793823242</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2416.667938232422</v>
+        <v>-2166.66539510091</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.41999816894531</v>
+        <v>37.2599983215332</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1775824578253777</v>
+        <v>-0.1810989379882812</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27413.91807248741</v>
+        <v>27296.70206705729</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-5919.415260845923</v>
+        <v>-6036.631266276039</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>408</v>
+        <v>401.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.09898989898989896</v>
+        <v>0.08148148148148149</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36632.99663299663</v>
+        <v>36049.38271604937</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3299.663299663298</v>
+        <v>2716.049382716046</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -3121,13 +3121,13 @@
         <v>46310</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>94963.58010058495</v>
+        <v>94512.75272133909</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0</v>
+        <v>-0.004747371347713969</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>-0.05036419899415057</v>
+        <v>-0.05487247278660912</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>12070.2001953125</v>
@@ -3136,11 +3136,34 @@
         <v>-0.1192206512468987</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>0.06885645225274817</v>
+        <v>0.06434817846028962</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>94512.75272133909</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>-0.05487247278660912</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>11721.7001953125</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>-0.1446511824786558</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.08977870969204671</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G99"/>
+  <autoFilter ref="A1:G100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -916,10 +916,10 @@
         <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018497320274815</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602344735420602</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608915285652106</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573839</v>
+        <v>-0.01516627338573817</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751684</v>
+        <v>0.01458616347751707</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955845</v>
+        <v>-0.06061085928955823</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.0008213118147898379</v>
+        <v>-0.00082131181479006</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551964</v>
+        <v>99701.94672551962</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621612</v>
+        <v>-0.007073005927621834</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.002980532744803588</v>
+        <v>-0.00298053274480381</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04874820607467067</v>
+        <v>-0.0487482060746709</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.00180034251077299</v>
+        <v>-0.001800342510772768</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409486</v>
+        <v>-0.01334406573409508</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.00366991614864931</v>
+        <v>0.003669916148649088</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968264</v>
+        <v>-0.03129799068968286</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180841</v>
+        <v>-0.01576249680180819</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425054</v>
+        <v>99094.94601425053</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.009050539857494599</v>
+        <v>-0.00905053985749471</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0562338154978187</v>
+        <v>-0.05623381549781881</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.00593839502983573</v>
+        <v>-0.005938395029835619</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956823</v>
+        <v>97308.67800956822</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614126</v>
+        <v>-0.02106911747614149</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431761</v>
+        <v>-0.02691321990431783</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787283</v>
+        <v>-0.06237731797787305</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982734163</v>
+        <v>-0.004314514982733941</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866686</v>
+        <v>0.02121828779866664</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711579</v>
+        <v>0.01156806056711557</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300097</v>
+        <v>-0.01586918403300119</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820384</v>
+        <v>0.03846461342820406</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235539</v>
+        <v>0.02467092015235517</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532714</v>
+        <v>0.04632805543532692</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0195475533921281</v>
+        <v>0.01954755339212788</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614189</v>
+        <v>-0.02556649570614167</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667342</v>
+        <v>95488.37939667344</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.04511620603326572</v>
+        <v>-0.0451162060332656</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361011</v>
+        <v>-0.07605607760361</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227376</v>
+        <v>97722.23537227378</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092787</v>
+        <v>-0.004717395579092676</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726242</v>
+        <v>-0.02277764627726231</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969083</v>
+        <v>-0.08097233395969072</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991624</v>
+        <v>98425.88257991623</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.006374778211714838</v>
+        <v>-0.00637477821171506</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083754</v>
+        <v>-0.01574117420083776</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903374</v>
+        <v>-0.07933574512903396</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939357</v>
+        <v>0.007072410694939579</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347899</v>
+        <v>97531.90369347902</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446696</v>
+        <v>-0.01604171927446674</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306521006</v>
+        <v>-0.02468096306520984</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.07066021068451822</v>
+        <v>-0.070660210684518</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471233</v>
+        <v>96900.04456471234</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556386</v>
+        <v>-0.006478486575556497</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.03099955435287671</v>
+        <v>-0.0309995543528766</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974184</v>
+        <v>-0.06930953683974173</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.006867825931805349</v>
+        <v>-0.00686782593180546</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759624</v>
+        <v>-0.01879633345759602</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756384</v>
+        <v>0.02619952629756406</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452455</v>
+        <v>-0.01260664742452433</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702301</v>
+        <v>-0.02504358406702312</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2937,13 +2937,13 @@
         <v>46300</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>96405.57674575874</v>
+        <v>96405.57674575872</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.01171654285041512</v>
+        <v>0.0117165428504149</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>-0.03594423254241264</v>
+        <v>-0.03594423254241286</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>12443.900390625</v>
@@ -2952,7 +2952,7 @@
         <v>-0.09195122660354638</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.05600699406113374</v>
+        <v>0.05600699406113352</v>
       </c>
     </row>
     <row r="92">
@@ -2963,7 +2963,7 @@
         <v>95484.05944327016</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.009558755142545339</v>
+        <v>-0.009558755142545117</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>-0.04515940556729836</v>
@@ -3006,13 +3006,13 @@
         <v>46303</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>94211.44754964461</v>
+        <v>94211.4475496446</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>0.009247100063994651</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.05788552450355389</v>
+        <v>-0.057885524503554</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>12213.599609375</v>
@@ -3021,7 +3021,7 @@
         <v>-0.1087565959300204</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.05087107142646652</v>
+        <v>0.05087107142646641</v>
       </c>
     </row>
     <row r="95">
@@ -3032,7 +3032,7 @@
         <v>95129.74844615087</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0.009747232638818826</v>
+        <v>0.009747232638819048</v>
       </c>
       <c r="D95" s="4" t="n">
         <v>-0.04870251553849125</v>
@@ -3052,13 +3052,13 @@
         <v>46307</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>94479.56742347739</v>
+        <v>94479.56742347738</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.006834676148035124</v>
+        <v>-0.006834676148035235</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.05520432576522616</v>
+        <v>-0.05520432576522627</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>12150.7001953125</v>
@@ -3067,7 +3067,7 @@
         <v>-0.1133464539322461</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.05814212816701991</v>
+        <v>0.0581421281670198</v>
       </c>
     </row>
     <row r="97">

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11721.7001953125</v>
+        <v>11430.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.05487247278660912</v>
+        <v>-0.09083738144244968</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1446511824786558</v>
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.08977870969204671</v>
+        <v>0.07509230263701616</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.40000152587891</v>
+        <v>36.2599983215332</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.06499996185302737</v>
+        <v>-0.09350004196166994</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>31166.66793823242</v>
+        <v>30216.66526794433</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2166.66539510091</v>
+        <v>-3116.668065388996</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.2599983215332</v>
+        <v>36.15999984741211</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.1810989379882812</v>
+        <v>-0.2052747286283053</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>27296.70206705729</v>
+        <v>26490.84237905648</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-6036.631266276039</v>
+        <v>-6842.490954276844</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>401.5</v>
+        <v>381</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.08148148148148149</v>
+        <v>0.02626262626262621</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>36049.38271604937</v>
+        <v>34208.7542087542</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2716.049382716046</v>
+        <v>875.4208754208739</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274815</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602344735420602</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652106</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -1215,10 +1215,10 @@
         <v>101458.6163477517</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01516627338573817</v>
+        <v>-0.01516627338573839</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.01458616347751707</v>
+        <v>0.01458616347751684</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>14734.5</v>
@@ -1227,7 +1227,7 @@
         <v>0.07519702276707529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.06061085928955823</v>
+        <v>-0.06061085928955845</v>
       </c>
     </row>
     <row r="17">
@@ -1238,7 +1238,7 @@
         <v>101375.287187433</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.00082131181479006</v>
+        <v>-0.0008213118147898379</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.0137528718743305</v>
@@ -1281,13 +1281,13 @@
         <v>46197</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>99701.94672551962</v>
+        <v>99701.94672551964</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.007073005927621834</v>
+        <v>-0.007073005927621612</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.00298053274480381</v>
+        <v>-0.002980532744803588</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>14331.2001953125</v>
@@ -1296,7 +1296,7 @@
         <v>0.04576767332986709</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.0487482060746709</v>
+        <v>-0.04874820607467067</v>
       </c>
     </row>
     <row r="20">
@@ -1307,7 +1307,7 @@
         <v>99522.44907242287</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.001800342510772768</v>
+        <v>-0.00180034251077299</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>-0.004775509275771306</v>
@@ -1353,10 +1353,10 @@
         <v>100366.9916148649</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01334406573409508</v>
+        <v>-0.01334406573409486</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.003669916148649088</v>
+        <v>0.00366991614864931</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>14183.2001953125</v>
@@ -1365,7 +1365,7 @@
         <v>0.03496790683833195</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.03129799068968286</v>
+        <v>-0.03129799068968264</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>98784.9572305285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01576249680180819</v>
+        <v>-0.01576249680180841</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>-0.01215042769471508</v>
@@ -1396,13 +1396,13 @@
         <v>46204</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>99094.94601425053</v>
+        <v>99094.94601425054</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.003138016074640149</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.00905053985749471</v>
+        <v>-0.009050539857494599</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>14350.599609375</v>
@@ -1411,7 +1411,7 @@
         <v>0.0471832756403241</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.05623381549781881</v>
+        <v>-0.0562338154978187</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1422,7 @@
         <v>98506.48107935768</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.005938395029835619</v>
+        <v>-0.00593839502983573</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>-0.01493518920642323</v>
@@ -1511,13 +1511,13 @@
         <v>46211</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>97308.67800956822</v>
+        <v>97308.67800956823</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.02106911747614149</v>
+        <v>-0.02106911747614126</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02691321990431783</v>
+        <v>-0.02691321990431761</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>14190</v>
@@ -1526,7 +1526,7 @@
         <v>0.03546409807355522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06237731797787305</v>
+        <v>-0.06237731797787283</v>
       </c>
     </row>
     <row r="30">
@@ -1537,7 +1537,7 @@
         <v>96888.8382603459</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.004314514982733941</v>
+        <v>-0.004314514982734163</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>-0.031111617396541</v>
@@ -1606,10 +1606,10 @@
         <v>101156.8060567116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02121828779866664</v>
+        <v>0.02121828779866686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01156806056711557</v>
+        <v>0.01156806056711579</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>14080</v>
@@ -1618,7 +1618,7 @@
         <v>0.02743724460011676</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.01586918403300119</v>
+        <v>-0.01586918403300097</v>
       </c>
     </row>
     <row r="34">
@@ -1629,7 +1629,7 @@
         <v>105047.7634973148</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03846461342820406</v>
+        <v>0.03846461342820384</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>0.05047763497314772</v>
@@ -1675,10 +1675,10 @@
         <v>104632.8055435327</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.02467092015235517</v>
+        <v>0.02467092015235539</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.04632805543532692</v>
+        <v>0.04632805543532714</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>14071</v>
@@ -1687,7 +1687,7 @@
         <v>0.02678050204319904</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.01954755339212788</v>
+        <v>0.0195475533921281</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>101957.7113698824</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>-0.02556649570614167</v>
+        <v>-0.02556649570614189</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.01957711369882409</v>
@@ -2155,13 +2155,13 @@
         <v>46252</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95488.37939667344</v>
+        <v>95488.37939667342</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>0.01565389108349602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>-0.0451162060332656</v>
+        <v>-0.04511620603326572</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>14128</v>
@@ -2170,7 +2170,7 @@
         <v>0.03093987157034439</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-0.07605607760361</v>
+        <v>-0.07605607760361011</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2247,13 @@
         <v>46258</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>97722.23537227378</v>
+        <v>97722.23537227376</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>-0.004717395579092676</v>
+        <v>-0.004717395579092787</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>-0.02277764627726231</v>
+        <v>-0.02277764627726242</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>14501.5</v>
@@ -2262,7 +2262,7 @@
         <v>0.05819468768242841</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-0.08097233395969072</v>
+        <v>-0.08097233395969083</v>
       </c>
     </row>
     <row r="62">
@@ -2316,13 +2316,13 @@
         <v>46261</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>98425.88257991623</v>
+        <v>98425.88257991624</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.00637477821171506</v>
+        <v>-0.006374778211714838</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.01574117420083776</v>
+        <v>-0.01574117420083754</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>14575.5</v>
@@ -2331,7 +2331,7 @@
         <v>0.0635945709281962</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.07933574512903396</v>
+        <v>-0.07933574512903374</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2342,7 @@
         <v>99121.99084453328</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.007072410694939579</v>
+        <v>0.007072410694939357</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>-0.008780091554667191</v>
@@ -2362,13 +2362,13 @@
         <v>46265</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>97531.90369347902</v>
+        <v>97531.90369347899</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.01604171927446674</v>
+        <v>-0.01604171927446696</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02468096306520984</v>
+        <v>-0.02468096306521006</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>14334.099609375</v>
@@ -2377,7 +2377,7 @@
         <v>0.04597924761930816</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.070660210684518</v>
+        <v>-0.07066021068451822</v>
       </c>
     </row>
     <row r="67">
@@ -2385,13 +2385,13 @@
         <v>46266</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>96900.04456471234</v>
+        <v>96900.04456471233</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>-0.006478486575556497</v>
+        <v>-0.006478486575556386</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>-0.0309995543528766</v>
+        <v>-0.03099955435287671</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>14229</v>
@@ -2400,7 +2400,7 @@
         <v>0.03830998248686512</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-0.06930953683974173</v>
+        <v>-0.06930953683974184</v>
       </c>
     </row>
     <row r="68">
@@ -2411,7 +2411,7 @@
         <v>96234.5519258577</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.00686782593180546</v>
+        <v>-0.006867825931805349</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>-0.03765448074142297</v>
@@ -2595,10 +2595,10 @@
         <v>102619.9526297564</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.01879633345759602</v>
+        <v>-0.01879633345759624</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.02619952629756406</v>
+        <v>0.02619952629756384</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>14235.7998046875</v>
@@ -2607,7 +2607,7 @@
         <v>0.03880617372208839</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.01260664742452433</v>
+        <v>-0.01260664742452455</v>
       </c>
     </row>
     <row r="77">
@@ -2618,7 +2618,7 @@
         <v>100049.9812191192</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>-0.02504358406702312</v>
+        <v>-0.02504358406702301</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>0.000499812191191662</v>
@@ -2937,13 +2937,13 @@
         <v>46300</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>96405.57674575872</v>
+        <v>96405.57674575874</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.0117165428504149</v>
+        <v>0.01171654285041512</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>-0.03594423254241286</v>
+        <v>-0.03594423254241264</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>12443.900390625</v>
@@ -2952,7 +2952,7 @@
         <v>-0.09195122660354638</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.05600699406113352</v>
+        <v>0.05600699406113374</v>
       </c>
     </row>
     <row r="92">
@@ -2963,7 +2963,7 @@
         <v>95484.05944327016</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.009558755142545117</v>
+        <v>-0.009558755142545339</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>-0.04515940556729836</v>
@@ -3006,13 +3006,13 @@
         <v>46303</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>94211.4475496446</v>
+        <v>94211.44754964461</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>0.009247100063994651</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.057885524503554</v>
+        <v>-0.05788552450355389</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>12213.599609375</v>
@@ -3021,7 +3021,7 @@
         <v>-0.1087565959300204</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.05087107142646641</v>
+        <v>0.05087107142646652</v>
       </c>
     </row>
     <row r="95">
@@ -3032,7 +3032,7 @@
         <v>95129.74844615087</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0.009747232638819048</v>
+        <v>0.009747232638818826</v>
       </c>
       <c r="D95" s="4" t="n">
         <v>-0.04870251553849125</v>
@@ -3052,13 +3052,13 @@
         <v>46307</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>94479.56742347738</v>
+        <v>94479.56742347739</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.006834676148035235</v>
+        <v>-0.006834676148035124</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.05520432576522627</v>
+        <v>-0.05520432576522616</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>12150.7001953125</v>
@@ -3067,7 +3067,7 @@
         <v>-0.1133464539322461</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.0581421281670198</v>
+        <v>0.05814212816701991</v>
       </c>
     </row>
     <row r="97">
@@ -3144,13 +3144,13 @@
         <v>46311</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>94512.75272133909</v>
+        <v>90916.26185575503</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0</v>
+        <v>-0.03805296917113321</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.05487247278660912</v>
+        <v>-0.09083738144244968</v>
       </c>
       <c r="E100" s="5" t="n">
         <v>11721.7001953125</v>
@@ -3159,11 +3159,34 @@
         <v>-0.1446511824786558</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.08977870969204671</v>
+        <v>0.05381380103620614</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>90916.26185575503</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>-0.09083738144244968</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>11430.099609375</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>-0.1659296840794658</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0.07509230263701616</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G100"/>
+  <autoFilter ref="A1:G101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11430.099609375</v>
+        <v>11797.7001953125</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.09083738144244968</v>
+        <v>-0.1099845490521673</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1659296840794658</v>
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.07509230263701616</v>
+        <v>0.02912080739029477</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.2599983215332</v>
+        <v>35.61999893188477</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.09350004196166994</v>
+        <v>-0.1095000267028808</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30216.66526794433</v>
+        <v>29683.3324432373</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-3116.668065388996</v>
+        <v>-3650.000890096027</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.15999984741211</v>
+        <v>35.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2052747286283053</v>
+        <v>-0.2197802197802198</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>26490.84237905648</v>
+        <v>26007.326007326</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-6842.490954276844</v>
+        <v>-7326.007326007326</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.02626262626262621</v>
+        <v>-0.0006734006734007147</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34208.7542087542</v>
+        <v>33310.88664421997</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>875.4208754208739</v>
+        <v>-22.44668911335611</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3167,13 +3167,13 @@
         <v>46314</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>90916.26185575503</v>
+        <v>89001.54509478329</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0</v>
+        <v>-0.02106022313158429</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>-0.09083738144244968</v>
+        <v>-0.1099845490521671</v>
       </c>
       <c r="E101" s="5" t="n">
         <v>11430.099609375</v>
@@ -3182,11 +3182,34 @@
         <v>-0.1659296840794658</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>0.07509230263701616</v>
+        <v>0.0559451350272987</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>89001.54509478329</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>-0.1099845490521671</v>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>11797.7001953125</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>-0.139105356442462</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0.02912080739029488</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G101"/>
+  <autoFilter ref="A1:G102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11797.7001953125</v>
+        <v>11577.099609375</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1099845490521673</v>
+        <v>-0.0785442002046236</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.139105356442462</v>
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02912080739029477</v>
+        <v>0.07665868877852</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>35.61999893188477</v>
+        <v>37.18000030517578</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1095000267028808</v>
+        <v>-0.07049999237060545</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>29683.3324432373</v>
+        <v>30983.33358764648</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-3650.000890096027</v>
+        <v>-2349.999745686848</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>35.5</v>
+        <v>36.2400016784668</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2197802197802198</v>
+        <v>-0.2035164466271033</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>26007.326007326</v>
+        <v>26549.45177909655</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-7326.007326007326</v>
+        <v>-6783.881554236777</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>371</v>
+        <v>385.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0006734006734007147</v>
+        <v>0.03838383838383841</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33310.88664421997</v>
+        <v>34612.79461279461</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-22.44668911335611</v>
+        <v>1279.461279461277</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3190,13 +3190,13 @@
         <v>46315</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>89001.54509478329</v>
+        <v>92145.57997953765</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0</v>
+        <v>0.03532562138562967</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.1099845490521671</v>
+        <v>-0.07854420020462349</v>
       </c>
       <c r="E102" s="5" t="n">
         <v>11797.7001953125</v>
@@ -3205,11 +3205,34 @@
         <v>-0.139105356442462</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.02912080739029488</v>
+        <v>0.06056115623783853</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>92145.57997953765</v>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>-0.07854420020462349</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>11577.099609375</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>-0.1552028889831436</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0.07665868877852011</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G102"/>
+  <autoFilter ref="A1:G103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11577.099609375</v>
+        <v>11220.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0785442002046236</v>
+        <v>-0.0912237107054652</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1552028889831436</v>
+        <v>-0.1812317286467455</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.07665868877852</v>
+        <v>0.09000801794128033</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>37.18000030517578</v>
+        <v>36.52000045776367</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.07049999237060545</v>
+        <v>-0.08699998855590818</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30983.33358764648</v>
+        <v>30433.33371480306</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2349.999745686848</v>
+        <v>-2899.999618530273</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.2400016784668</v>
+        <v>35.2599983215332</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2035164466271033</v>
+        <v>-0.2250549819443252</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>26549.45177909655</v>
+        <v>25831.50060185582</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-6783.881554236777</v>
+        <v>-7501.832731477505</v>
       </c>
     </row>
     <row r="4">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3213,13 +3213,13 @@
         <v>46316</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>92145.57997953765</v>
+        <v>90877.62892945351</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0</v>
+        <v>-0.01376030245146553</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>-0.07854420020462349</v>
+        <v>-0.09122371070546498</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>11577.099609375</v>
@@ -3228,11 +3228,34 @@
         <v>-0.1552028889831436</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>0.07665868877852011</v>
+        <v>0.06397917827767863</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>90877.62892945351</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>-0.09122371070546498</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>11220.400390625</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>-0.1812317286467455</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>0.09000801794128055</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G103"/>
+  <autoFilter ref="A1:G104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11220.400390625</v>
+        <v>11117</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0912237107054652</v>
+        <v>-0.1265165383178767</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1812317286467455</v>
+        <v>-0.1887769994162288</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.09000801794128033</v>
+        <v>0.06226046109835215</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>36.52000045776367</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.08699998855590818</v>
+        <v>-0.1225000381469726</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>30433.33371480306</v>
+        <v>29249.99872843424</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-2899.999618530273</v>
+        <v>-4083.334604899086</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>35.2599983215332</v>
+        <v>34.08000183105469</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2250549819443252</v>
+        <v>-0.2509889707460509</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>25831.50060185582</v>
+        <v>24967.03430846497</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-7501.832731477505</v>
+        <v>-8366.29902486836</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>385.5</v>
+        <v>369</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.03838383838383841</v>
+        <v>-0.0060606060606061</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>34612.79461279461</v>
+        <v>33131.31313131312</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1279.461279461277</v>
+        <v>-202.020202020205</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3236,13 +3236,13 @@
         <v>46317</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>90877.62892945351</v>
+        <v>87348.34616821235</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0</v>
+        <v>-0.03883555064999411</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.09122371070546498</v>
+        <v>-0.1265165383178766</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>11220.400390625</v>
@@ -3251,11 +3251,34 @@
         <v>-0.1812317286467455</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.09000801794128055</v>
+        <v>0.05471519032886896</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>87348.34616821235</v>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>-0.1265165383178766</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>11117</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>-0.1887769994162288</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>0.06226046109835226</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G104"/>
+  <autoFilter ref="A1:G105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11117</v>
+        <v>11152</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1265165383178767</v>
+        <v>-0.153556925886336</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.06226046109835215</v>
+        <v>0.03266607469743521</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>35.09999847412109</v>
+        <v>31.60000038146973</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1225000381469726</v>
+        <v>-0.2099999904632568</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>29249.99872843424</v>
+        <v>26333.33365122477</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-4083.334604899086</v>
+        <v>-6999.999682108559</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>34.08000183105469</v>
+        <v>33.88000106811523</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2509889707460509</v>
+        <v>-0.2553845919095553</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>24967.03430846497</v>
+        <v>24820.51360301482</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-8366.29902486836</v>
+        <v>-8512.819730318508</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0060606060606061</v>
+        <v>0.00471380471380467</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33131.31313131312</v>
+        <v>33490.46015712681</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-202.020202020205</v>
+        <v>157.1268237934855</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -3259,13 +3259,13 @@
         <v>46318</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>87348.34616821235</v>
+        <v>84644.30741136642</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0</v>
+        <v>-0.030956954258053</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>-0.1265165383178766</v>
+        <v>-0.1535569258863358</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>11117</v>
@@ -3274,11 +3274,34 @@
         <v>-0.1887769994162288</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>0.06226046109835226</v>
+        <v>0.03522007352989298</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>84644.30741136642</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>-0.1535569258863358</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>11152</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>-0.1862230005837712</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>0.03266607469743532</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G105"/>
+  <autoFilter ref="A1:G106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11152</v>
+        <v>11151</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.153556925886336</v>
+        <v>-0.1545672621357488</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.03266607469743521</v>
+        <v>0.0317287098432355</v>
       </c>
     </row>
     <row r="19">
@@ -692,7 +692,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>31.60000038146973</v>
+        <v>30.86000061035156</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.2099999904632568</v>
+        <v>-0.2284999847412109</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>26333.33365122477</v>
+        <v>25716.66717529297</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-6999.999682108559</v>
+        <v>-7616.666158040363</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>33.88000106811523</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2553845919095553</v>
+        <v>-0.2439560104202438</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>24820.51360301482</v>
+        <v>25201.4663193252</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-8512.819730318508</v>
+        <v>-8131.867014008127</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>373</v>
+        <v>374.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.00471380471380467</v>
+        <v>0.008754208754208737</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33490.46015712681</v>
+        <v>33625.14029180695</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>157.1268237934855</v>
+        <v>291.8069584736222</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.4973202748</v>
+        <v>102018.5000603492</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018497320274837</v>
+        <v>0.02018500060349204</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.0160234473542058</v>
+        <v>-0.01602341995346213</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608915285652328</v>
+        <v>-0.006608941966748882</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42505243311</v>
+        <v>98363.42779250747</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960480234594943</v>
+        <v>-0.003960452488282362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636574947566882</v>
+        <v>-0.01636572207492526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932835961686852</v>
+        <v>-0.01932833221612495</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82176630478</v>
+        <v>97767.82450637914</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129595282427</v>
+        <v>-0.006055129426606909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232178233695215</v>
+        <v>-0.02232175493620858</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520415244786856</v>
+        <v>-0.02520412504712499</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597117489406608</v>
+        <v>0.01597114642011177</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7390924518</v>
+        <v>102473.7418325262</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165682937409042</v>
+        <v>0.03165685695985476</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473739092451832</v>
+        <v>0.02473741832526177</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943660138612092</v>
+        <v>-0.02943657398537747</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.00940670518799358</v>
+        <v>-0.009406731675747682</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -3282,13 +3282,13 @@
         <v>46321</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>84644.30741136642</v>
+        <v>84543.27378642514</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0</v>
+        <v>-0.001193625750285476</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.1535569258863358</v>
+        <v>-0.1545672621357487</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>11152</v>
@@ -3297,11 +3297,34 @@
         <v>-0.1862230005837712</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.03266607469743532</v>
+        <v>0.0316557384480225</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>84543.27378642514</v>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>-0.1545672621357487</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>11151</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>-0.1862959719789843</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>0.03172870984323561</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G106"/>
+  <autoFilter ref="A1:G107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11151</v>
+        <v>11165.400390625</v>
       </c>
     </row>
     <row r="9">
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1545672621357488</v>
+        <v>-0.1645814200072547</v>
       </c>
     </row>
     <row r="17">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.0317287098432355</v>
+        <v>0.02066373537620991</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>30.86000061035156</v>
+        <v>31.45999908447266</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.2284999847412109</v>
+        <v>-0.2135000228881836</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>25716.66717529297</v>
+        <v>26216.66590372721</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-7616.666158040363</v>
+        <v>-7116.667429606117</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>34.40000152587891</v>
+        <v>33.7599983215332</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2439560104202438</v>
+        <v>-0.2580220149113581</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>25201.4663193252</v>
+        <v>24732.59950295473</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-8131.867014008127</v>
+        <v>-8600.733830378602</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>374.5</v>
+        <v>363</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.008754208754208737</v>
+        <v>-0.02222222222222225</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>33625.14029180695</v>
+        <v>32592.59259259259</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>291.8069584736222</v>
+        <v>-740.7407407407409</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3305,13 +3305,13 @@
         <v>46322</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>84543.27378642514</v>
+        <v>83541.85799927454</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0</v>
+        <v>-0.01184500838801661</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>-0.1545672621357487</v>
+        <v>-0.1645814200072546</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>11151</v>
@@ -3320,11 +3320,34 @@
         <v>-0.1862959719789843</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>0.03172870984323561</v>
+        <v>0.02171455197172967</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>83541.85799927454</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>-0.1645814200072546</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>11165.400390625</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>-0.1852451553834646</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0.02066373537621002</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G107"/>
+  <autoFilter ref="A1:G108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1645814200072547</v>
+        <v>-0.1639844853612701</v>
       </c>
     </row>
     <row r="17">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02066373537620991</v>
+        <v>0.02126067002219456</v>
       </c>
     </row>
     <row r="19">
@@ -753,19 +753,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>31.45999908447266</v>
+        <v>31.21999931335449</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.2135000228881836</v>
+        <v>-0.2195000171661377</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>26216.66590372721</v>
+        <v>26016.66609446207</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>-7116.667429606117</v>
+        <v>-7316.667238871254</v>
       </c>
     </row>
     <row r="3">
@@ -781,19 +781,19 @@
         <v>45.5</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>33.7599983215332</v>
+        <v>33.90000152587891</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.2580220149113581</v>
+        <v>-0.2549450214092548</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>24732.59950295473</v>
+        <v>24835.16595302484</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>-8600.733830378602</v>
+        <v>-8498.167380308492</v>
       </c>
     </row>
     <row r="4">
@@ -809,19 +809,19 @@
         <v>371.25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>363</v>
+        <v>364.75</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.02222222222222225</v>
+        <v>-0.01750841750841747</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>33333.33333333333</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32592.59259259259</v>
+        <v>32749.71941638608</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-740.7407407407409</v>
+        <v>-583.6139169472481</v>
       </c>
     </row>
   </sheetData>
@@ -913,13 +913,13 @@
         <v>46175</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>102018.5000603492</v>
+        <v>102018.4973202748</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02018500060349204</v>
+        <v>0.02018497320274837</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>14200.2001953125</v>
@@ -928,7 +928,7 @@
         <v>0.03620842055695417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.01602341995346213</v>
+        <v>-0.0160234473542058</v>
       </c>
     </row>
     <row r="4">
@@ -939,7 +939,7 @@
         <v>101344.2657139156</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.006608941966748882</v>
+        <v>-0.006608915285652328</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.01344265713915593</v>
@@ -1051,13 +1051,13 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98363.42779250747</v>
+        <v>98363.42505243311</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.003960452488282362</v>
+        <v>-0.003960480234594943</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01636572207492526</v>
+        <v>-0.01636574947566882</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>13744.599609375</v>
@@ -1066,7 +1066,7 @@
         <v>0.002962610141199695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01932833221612495</v>
+        <v>-0.01932835961686852</v>
       </c>
     </row>
     <row r="10">
@@ -1074,13 +1074,13 @@
         <v>46184</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97767.82450637914</v>
+        <v>97767.82176630478</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.006055129426606909</v>
+        <v>-0.006055129595282427</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02232175493620858</v>
+        <v>-0.02232178233695215</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>13743.5</v>
@@ -1089,7 +1089,7 @@
         <v>0.00288237011091641</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.02520412504712499</v>
+        <v>-0.02520415244786856</v>
       </c>
     </row>
     <row r="11">
@@ -1100,7 +1100,7 @@
         <v>99329.28874674633</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01597114642011177</v>
+        <v>0.01597117489406608</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>-0.006707112532536752</v>
@@ -1120,13 +1120,13 @@
         <v>46188</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>102473.7418325262</v>
+        <v>102473.7390924518</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03165685695985476</v>
+        <v>0.03165682937409042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02473741832526177</v>
+        <v>0.02473739092451832</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>14446.400390625</v>
@@ -1135,7 +1135,7 @@
         <v>0.05417399231063924</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02943657398537747</v>
+        <v>-0.02943660138612092</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1146,7 @@
         <v>101509.7988392978</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.009406731675747682</v>
+        <v>-0.00940670518799358</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.0150979883929776</v>
@@ -3328,13 +3328,13 @@
         <v>46323</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>83541.85799927454</v>
+        <v>83601.55146387299</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0</v>
+        <v>0.0007145336006169067</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.1645814200072546</v>
+        <v>-0.1639844853612701</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>11165.400390625</v>
@@ -3343,7 +3343,7 @@
         <v>-0.1852451553834646</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.02066373537621002</v>
+        <v>0.02126067002219456</v>
       </c>
     </row>
   </sheetData>

--- a/reports/one_month_follow_up.xlsx
+++ b/reports/one_month_follow_up.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TAKIP_OZETI'!$A$1:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POZISYONLAR'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'GUNLUK_TAKIP'!$A$1:$G$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NOTLAR'!$A$1:$A$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11165.400390625</v>
+        <v>10759.599609375</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1852451553834646</v>
+        <v>-0.2148570045698336</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.02126067002219456</v>
+        <v>0.0508725192085635</v>
       </c>
     </row>
     <row r="19">
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3346,8 +3346,31 @@
         <v>0.02126067002219456</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="6" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>83601.55146387299</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>-0.1639844853612701</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>10759.599609375</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>-0.2148570045698336</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>0.0508725192085635</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G108"/>
+  <autoFilter ref="A1:G109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
